--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -9,10 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="主线副本" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,8 +64,40 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="G3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+组合掉落</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="263">
   <si>
     <t>_Id</t>
   </si>
@@ -796,6 +829,63 @@
   </si>
   <si>
     <t>30001,180072</t>
+  </si>
+  <si>
+    <t>DropLayerList</t>
+  </si>
+  <si>
+    <t>BaseLayerList</t>
+  </si>
+  <si>
+    <t>2073,4007,5013,3004</t>
+  </si>
+  <si>
+    <t>1,0,0,0</t>
+  </si>
+  <si>
+    <t>30,5000,5000,8000</t>
+  </si>
+  <si>
+    <t>30001,180073</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>2074,4007,5013,3004</t>
+  </si>
+  <si>
+    <t>2075,4007,5013,3004</t>
+  </si>
+  <si>
+    <t>2076,4007,5013,3004</t>
+  </si>
+  <si>
+    <t>2077,4007,5013,3004</t>
+  </si>
+  <si>
+    <t>2078,4007,5013,3004</t>
+  </si>
+  <si>
+    <t>2,0,0,0</t>
+  </si>
+  <si>
+    <t>3,0,0,0</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>4,0,0,0</t>
+  </si>
+  <si>
+    <t>5,0,0,0</t>
+  </si>
+  <si>
+    <t>6,0,0,0</t>
+  </si>
+  <si>
+    <t>7,0,0,0</t>
   </si>
 </sst>
 </file>
@@ -808,7 +898,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -832,6 +922,11 @@
     <font>
       <sz val="9"/>
       <color rgb="FF0F1115"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1321,16 +1416,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1339,123 +1431,126 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1468,7 +1563,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1484,12 +1578,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1850,16 +1950,16 @@
   <dimension ref="C3:L77"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25454545454545" style="3" customWidth="1"/>
-    <col min="4" max="6" width="11.6272727272727" style="3" customWidth="1"/>
-    <col min="7" max="7" width="42.7272727272727" style="3" customWidth="1"/>
-    <col min="8" max="8" width="31.1818181818182" style="3" customWidth="1"/>
-    <col min="9" max="9" width="34.0909090909091" style="3" customWidth="1"/>
-    <col min="10" max="10" width="31.1818181818182" style="3" customWidth="1"/>
-    <col min="11" max="11" width="34.0909090909091" style="3" customWidth="1"/>
-    <col min="12" max="12" width="31.1818181818182" style="3" customWidth="1"/>
-    <col min="13" max="16380" width="9.25454545454545" style="3" customWidth="1"/>
-    <col min="16381" max="16384" width="9.25454545454545" style="3"/>
+    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="4" max="6" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="7" max="7" width="42.7272727272727" style="1" customWidth="1"/>
+    <col min="8" max="8" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.0909090909091" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34.0909090909091" style="1" customWidth="1"/>
+    <col min="12" max="12" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="13" max="16380" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="16381" max="16384" width="9.25454545454545" style="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="3:12">
@@ -1959,2127 +2059,2127 @@
       </c>
     </row>
     <row r="6" customHeight="1" spans="3:12">
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="3">
+      <c r="J6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="1">
         <v>100</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:12">
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="3">
+      <c r="J7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="1">
         <v>100</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:12">
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="J8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="1">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:12">
-      <c r="C9" s="3">
+      <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="J9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K9" s="1">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:12">
-      <c r="C10" s="3">
+      <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="J10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="1">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C11" s="1">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C11" s="2">
         <v>6</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>1</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="3">
+      <c r="J11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="1">
         <v>100</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
-      <c r="C12" s="3">
+      <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="J12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="1">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="3">
+      <c r="J13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K13" s="1">
         <v>100</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:12">
-      <c r="C14" s="3">
+      <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:12">
-      <c r="C15" s="3">
+      <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="J15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K15" s="1">
         <v>100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:12">
-      <c r="C16" s="3">
+      <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K16" s="3">
+      <c r="I16" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1">
         <v>100</v>
       </c>
-      <c r="L16" s="3">
+      <c r="L16" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C17" s="1">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C17" s="2">
         <v>12</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>2</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="J17" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K17" s="1">
         <v>100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="3:12">
-      <c r="C18" s="3">
+      <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="1">
         <v>3</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="J18" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="1">
         <v>100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="3:12">
-      <c r="C19" s="3">
+      <c r="C19" s="1">
         <v>14</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K19" s="3">
+      <c r="I19" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K19" s="1">
         <v>100</v>
       </c>
-      <c r="L19" s="3">
+      <c r="L19" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="3:12">
-      <c r="C20" s="3">
+      <c r="C20" s="1">
         <v>15</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="1">
         <v>3</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I20" s="17" t="s">
+      <c r="I20" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="J20" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="1">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="21" customHeight="1" spans="3:12">
-      <c r="C21" s="3">
+      <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="1">
         <v>3</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="J21" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="J21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="1">
         <v>100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="3:12">
-      <c r="C22" s="3">
+      <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="1">
         <v>3</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="J22" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="J22" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K22" s="1">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C23" s="1">
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C23" s="2">
         <v>18</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>3</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <v>3</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="19" t="s">
+      <c r="I23" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="J23" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="1">
         <v>100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C24" s="2">
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C24" s="3">
         <v>19</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="3">
         <v>4</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="J24" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="J24" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="1">
         <v>80</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="3:12">
-      <c r="C25" s="3">
+      <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="1">
         <v>4</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="H25" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="J25" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K25" s="3">
+      <c r="J25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="1">
         <v>80</v>
       </c>
-      <c r="L25" s="3">
+      <c r="L25" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="3:12">
-      <c r="C26" s="3">
+      <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="1">
         <v>4</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="H26" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="J26" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="J26" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="1">
         <v>80</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="3:12">
-      <c r="C27" s="3">
+      <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="H27" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="J27" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="J27" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="1">
         <v>80</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:12">
-      <c r="C28" s="3">
+      <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="1">
         <v>4</v>
       </c>
-      <c r="G28" s="16" t="s">
+      <c r="G28" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="J28" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K28" s="3">
+      <c r="J28" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="1">
         <v>80</v>
       </c>
-      <c r="L28" s="3">
+      <c r="L28" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C29" s="1">
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C29" s="2">
         <v>24</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="2">
         <v>4</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <v>4</v>
       </c>
-      <c r="G29" s="18" t="s">
+      <c r="G29" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="I29" s="19" t="s">
+      <c r="I29" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="J29" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="J29" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="1">
         <v>80</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C30" s="2">
+    <row r="30" s="3" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C30" s="3">
         <v>25</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="3">
         <v>5</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="I30" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="J30" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K30" s="3">
+      <c r="J30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K30" s="1">
         <v>80</v>
       </c>
-      <c r="L30" s="3">
+      <c r="L30" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="3:12">
-      <c r="C31" s="3">
+      <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="1">
         <v>5</v>
       </c>
-      <c r="G31" s="16" t="s">
+      <c r="G31" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="H31" s="20" t="s">
+      <c r="H31" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I31" s="17" t="s">
+      <c r="I31" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="J31" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K31" s="3">
+      <c r="J31" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K31" s="1">
         <v>80</v>
       </c>
-      <c r="L31" s="3">
+      <c r="L31" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:12">
-      <c r="C32" s="3">
+      <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="1">
         <v>5</v>
       </c>
-      <c r="G32" s="16" t="s">
+      <c r="G32" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I32" s="17" t="s">
+      <c r="I32" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="J32" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="J32" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K32" s="1">
         <v>80</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="3:12">
-      <c r="C33" s="3">
+      <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="1">
         <v>5</v>
       </c>
-      <c r="G33" s="16" t="s">
+      <c r="G33" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="H33" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="I33" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="J33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K33" s="1">
         <v>80</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="3:12">
-      <c r="C34" s="3">
+      <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="1">
         <v>5</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="G34" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="20" t="s">
+      <c r="H34" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I34" s="17" t="s">
+      <c r="I34" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="J34" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K34" s="3">
+      <c r="J34" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K34" s="1">
         <v>80</v>
       </c>
-      <c r="L34" s="3">
+      <c r="L34" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C35" s="1">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="2">
         <v>30</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>5</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <v>5</v>
       </c>
-      <c r="G35" s="18" t="s">
+      <c r="G35" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="H35" s="20" t="s">
+      <c r="H35" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="I35" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="J35" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K35" s="1">
         <v>80</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="3:12">
-      <c r="C36" s="3">
+      <c r="C36" s="1">
         <v>31</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="1">
         <v>6</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I36" s="17" t="s">
+      <c r="I36" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="J36" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K36" s="3">
+      <c r="J36" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K36" s="1">
         <v>80</v>
       </c>
-      <c r="L36" s="3">
+      <c r="L36" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="3:12">
-      <c r="C37" s="3">
+      <c r="C37" s="1">
         <v>32</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E37" s="1">
         <v>6</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="G37" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="I37" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="J37" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K37" s="3">
+      <c r="J37" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K37" s="1">
         <v>80</v>
       </c>
-      <c r="L37" s="3">
+      <c r="L37" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="3:12">
-      <c r="C38" s="3">
+      <c r="C38" s="1">
         <v>33</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="1">
         <v>6</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="G38" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="H38" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I38" s="17" t="s">
+      <c r="I38" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="J38" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K38" s="3">
+      <c r="J38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="1">
         <v>80</v>
       </c>
-      <c r="L38" s="3">
+      <c r="L38" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="3:12">
-      <c r="C39" s="3">
+      <c r="C39" s="1">
         <v>34</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="1">
         <v>6</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="G39" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="I39" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="J39" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K39" s="3">
+      <c r="J39" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K39" s="1">
         <v>80</v>
       </c>
-      <c r="L39" s="3">
+      <c r="L39" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:12">
-      <c r="C40" s="3">
+      <c r="C40" s="1">
         <v>35</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="E40" s="3">
+      <c r="E40" s="1">
         <v>6</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="G40" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="H40" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I40" s="17" t="s">
+      <c r="I40" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="J40" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K40" s="3">
+      <c r="J40" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K40" s="1">
         <v>80</v>
       </c>
-      <c r="L40" s="3">
+      <c r="L40" s="1">
         <v>80</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C41" s="1">
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C41" s="2">
         <v>36</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>6</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <v>6</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="I41" s="19" t="s">
+      <c r="I41" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="J41" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="J41" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K41" s="1">
         <v>80</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="1">
         <v>80</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:12">
-      <c r="C42" s="3">
+      <c r="C42" s="1">
         <v>37</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E42" s="1">
         <v>7</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="G42" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="I42" s="21" t="s">
+      <c r="I42" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="J42" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K42" s="3">
-        <v>60</v>
-      </c>
-      <c r="L42" s="3">
+      <c r="J42" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="1">
+        <v>60</v>
+      </c>
+      <c r="L42" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:12">
-      <c r="C43" s="3">
+      <c r="C43" s="1">
         <v>38</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="1">
         <v>7</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="G43" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="H43" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="I43" s="21" t="s">
+      <c r="I43" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="J43" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" s="3">
-        <v>60</v>
-      </c>
-      <c r="L43" s="3">
+      <c r="J43" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K43" s="1">
+        <v>60</v>
+      </c>
+      <c r="L43" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="3:12">
-      <c r="C44" s="3">
+      <c r="C44" s="1">
         <v>39</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="1">
         <v>7</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="G44" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H44" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="I44" s="21" t="s">
+      <c r="I44" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="J44" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K44" s="3">
-        <v>60</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="J44" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K44" s="1">
+        <v>60</v>
+      </c>
+      <c r="L44" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="3:12">
-      <c r="C45" s="3">
+      <c r="C45" s="1">
         <v>40</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="1">
         <v>7</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="G45" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="I45" s="21" t="s">
+      <c r="I45" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="J45" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K45" s="3">
-        <v>60</v>
-      </c>
-      <c r="L45" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" s="3" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C46" s="3">
+      <c r="J45" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K45" s="1">
+        <v>60</v>
+      </c>
+      <c r="L45" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="1">
         <v>41</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="1">
         <v>7</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="16" t="s">
+      <c r="F46" s="1"/>
+      <c r="G46" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="H46" s="16" t="s">
+      <c r="H46" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="I46" s="21" t="s">
+      <c r="I46" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="J46" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" s="3">
-        <v>60</v>
-      </c>
-      <c r="L46" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C47" s="1">
+      <c r="J46" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="1">
+        <v>60</v>
+      </c>
+      <c r="L46" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C47" s="2">
         <v>42</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="2">
         <v>7</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <v>7</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="H47" s="18" t="s">
+      <c r="H47" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="I47" s="19" t="s">
+      <c r="I47" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="J47" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K47" s="1">
-        <v>60</v>
-      </c>
-      <c r="L47" s="1">
+      <c r="J47" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K47" s="2">
+        <v>60</v>
+      </c>
+      <c r="L47" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="3:12">
-      <c r="C48" s="3">
+      <c r="C48" s="1">
         <v>43</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="1">
         <v>8</v>
       </c>
-      <c r="G48" s="16" t="s">
+      <c r="G48" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="H48" s="16" t="s">
+      <c r="H48" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="21" t="s">
+      <c r="I48" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="J48" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K48" s="3">
-        <v>60</v>
-      </c>
-      <c r="L48" s="3">
+      <c r="J48" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K48" s="1">
+        <v>60</v>
+      </c>
+      <c r="L48" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="3:12">
-      <c r="C49" s="3">
+      <c r="C49" s="1">
         <v>44</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E49" s="1">
         <v>8</v>
       </c>
-      <c r="G49" s="16" t="s">
+      <c r="G49" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="H49" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="I49" s="21" t="s">
+      <c r="I49" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="J49" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K49" s="3">
-        <v>60</v>
-      </c>
-      <c r="L49" s="3">
+      <c r="J49" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K49" s="1">
+        <v>60</v>
+      </c>
+      <c r="L49" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="3:12">
-      <c r="C50" s="3">
+      <c r="C50" s="1">
         <v>45</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E50" s="1">
         <v>8</v>
       </c>
-      <c r="G50" s="16" t="s">
+      <c r="G50" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="H50" s="16" t="s">
+      <c r="H50" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="I50" s="21" t="s">
+      <c r="I50" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="J50" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K50" s="3">
-        <v>60</v>
-      </c>
-      <c r="L50" s="3">
+      <c r="J50" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K50" s="1">
+        <v>60</v>
+      </c>
+      <c r="L50" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="3:12">
-      <c r="C51" s="3">
+      <c r="C51" s="1">
         <v>46</v>
       </c>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E51" s="1">
         <v>8</v>
       </c>
-      <c r="G51" s="16" t="s">
+      <c r="G51" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H51" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="I51" s="21" t="s">
+      <c r="I51" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="J51" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K51" s="3">
-        <v>60</v>
-      </c>
-      <c r="L51" s="3">
+      <c r="J51" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K51" s="1">
+        <v>60</v>
+      </c>
+      <c r="L51" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="3:12">
-      <c r="C52" s="3">
+      <c r="C52" s="1">
         <v>47</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="1">
         <v>8</v>
       </c>
-      <c r="G52" s="16" t="s">
+      <c r="G52" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="16" t="s">
+      <c r="H52" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="I52" s="21" t="s">
+      <c r="I52" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="J52" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K52" s="3">
-        <v>60</v>
-      </c>
-      <c r="L52" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C53" s="1">
+      <c r="J52" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" s="1">
+        <v>60</v>
+      </c>
+      <c r="L52" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C53" s="2">
         <v>48</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>8</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <v>8</v>
       </c>
-      <c r="G53" s="18" t="s">
+      <c r="G53" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="H53" s="18" t="s">
+      <c r="H53" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="I53" s="19" t="s">
+      <c r="I53" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="J53" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K53" s="1">
-        <v>60</v>
-      </c>
-      <c r="L53" s="1">
+      <c r="J53" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" s="2">
+        <v>60</v>
+      </c>
+      <c r="L53" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:12">
-      <c r="C54" s="3">
+      <c r="C54" s="1">
         <v>49</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="E54" s="3">
+      <c r="E54" s="1">
         <v>9</v>
       </c>
-      <c r="G54" s="17" t="s">
+      <c r="G54" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="16" t="s">
+      <c r="H54" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="I54" s="19" t="s">
+      <c r="I54" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="J54" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K54" s="3">
-        <v>60</v>
-      </c>
-      <c r="L54" s="3">
+      <c r="J54" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" s="1">
+        <v>60</v>
+      </c>
+      <c r="L54" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="3:12">
-      <c r="C55" s="3">
+      <c r="C55" s="1">
         <v>50</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E55" s="1">
         <v>9</v>
       </c>
-      <c r="G55" s="17" t="s">
+      <c r="G55" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="I55" s="19" t="s">
+      <c r="I55" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="J55" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K55" s="3">
-        <v>60</v>
-      </c>
-      <c r="L55" s="3">
+      <c r="J55" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K55" s="1">
+        <v>60</v>
+      </c>
+      <c r="L55" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="3:12">
-      <c r="C56" s="3">
+      <c r="C56" s="1">
         <v>51</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E56" s="1">
         <v>9</v>
       </c>
-      <c r="G56" s="17" t="s">
+      <c r="G56" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="I56" s="19" t="s">
+      <c r="I56" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="J56" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K56" s="3">
-        <v>60</v>
-      </c>
-      <c r="L56" s="3">
+      <c r="J56" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K56" s="1">
+        <v>60</v>
+      </c>
+      <c r="L56" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="3:12">
-      <c r="C57" s="3">
+      <c r="C57" s="1">
         <v>52</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="1">
         <v>9</v>
       </c>
-      <c r="G57" s="17" t="s">
+      <c r="G57" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H57" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="I57" s="19" t="s">
+      <c r="I57" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="J57" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K57" s="3">
-        <v>60</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="J57" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" s="1">
+        <v>60</v>
+      </c>
+      <c r="L57" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:12">
-      <c r="C58" s="3">
+      <c r="C58" s="1">
         <v>53</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="E58" s="3">
+      <c r="E58" s="1">
         <v>9</v>
       </c>
-      <c r="G58" s="17" t="s">
+      <c r="G58" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="H58" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="I58" s="19" t="s">
+      <c r="I58" s="22" t="s">
         <v>183</v>
       </c>
-      <c r="J58" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K58" s="3">
-        <v>60</v>
-      </c>
-      <c r="L58" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C59" s="1">
+      <c r="J58" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" s="1">
+        <v>60</v>
+      </c>
+      <c r="L58" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C59" s="2">
         <v>54</v>
       </c>
       <c r="D59" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>9</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <v>9</v>
       </c>
-      <c r="G59" s="19" t="s">
+      <c r="G59" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="H59" s="18" t="s">
+      <c r="H59" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="I59" s="19" t="s">
+      <c r="I59" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="J59" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K59" s="1">
-        <v>60</v>
-      </c>
-      <c r="L59" s="1">
+      <c r="J59" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" s="2">
+        <v>60</v>
+      </c>
+      <c r="L59" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="3:12">
-      <c r="C60" s="3">
+      <c r="C60" s="1">
         <v>55</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E60" s="3">
+      <c r="E60" s="1">
         <v>10</v>
       </c>
-      <c r="G60" s="17" t="s">
+      <c r="G60" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="H60" s="16" t="s">
+      <c r="H60" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="I60" s="19" t="s">
+      <c r="I60" s="22" t="s">
         <v>190</v>
       </c>
-      <c r="J60" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K60" s="3">
-        <v>60</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="J60" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K60" s="1">
+        <v>60</v>
+      </c>
+      <c r="L60" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="3:12">
-      <c r="C61" s="3">
+      <c r="C61" s="1">
         <v>56</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="E61" s="3">
+      <c r="E61" s="1">
         <v>10</v>
       </c>
-      <c r="G61" s="17" t="s">
+      <c r="G61" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="H61" s="16" t="s">
+      <c r="H61" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="I61" s="19" t="s">
+      <c r="I61" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="J61" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K61" s="3">
-        <v>60</v>
-      </c>
-      <c r="L61" s="3">
+      <c r="J61" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K61" s="1">
+        <v>60</v>
+      </c>
+      <c r="L61" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="3:12">
-      <c r="C62" s="3">
+      <c r="C62" s="1">
         <v>57</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="1">
         <v>10</v>
       </c>
-      <c r="G62" s="17" t="s">
+      <c r="G62" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="H62" s="16" t="s">
+      <c r="H62" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="I62" s="19" t="s">
+      <c r="I62" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="J62" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K62" s="3">
-        <v>60</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="J62" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K62" s="1">
+        <v>60</v>
+      </c>
+      <c r="L62" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="3:12">
-      <c r="C63" s="3">
+      <c r="C63" s="1">
         <v>58</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="E63" s="3">
+      <c r="E63" s="1">
         <v>10</v>
       </c>
-      <c r="G63" s="17" t="s">
+      <c r="G63" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="H63" s="16" t="s">
+      <c r="H63" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="I63" s="19" t="s">
+      <c r="I63" s="22" t="s">
         <v>199</v>
       </c>
-      <c r="J63" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K63" s="3">
-        <v>60</v>
-      </c>
-      <c r="L63" s="3">
+      <c r="J63" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K63" s="1">
+        <v>60</v>
+      </c>
+      <c r="L63" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="3:12">
-      <c r="C64" s="3">
+      <c r="C64" s="1">
         <v>59</v>
       </c>
       <c r="D64" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E64" s="1">
         <v>10</v>
       </c>
-      <c r="G64" s="17" t="s">
+      <c r="G64" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="H64" s="16" t="s">
+      <c r="H64" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="I64" s="19" t="s">
+      <c r="I64" s="22" t="s">
         <v>202</v>
       </c>
-      <c r="J64" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K64" s="3">
-        <v>60</v>
-      </c>
-      <c r="L64" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C65" s="1">
-        <v>60</v>
-      </c>
-      <c r="D65" s="11" t="s">
+      <c r="J64" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K64" s="1">
+        <v>60</v>
+      </c>
+      <c r="L64" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C65" s="2">
+        <v>60</v>
+      </c>
+      <c r="D65" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65" s="2">
         <v>10</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="2">
         <v>10</v>
       </c>
-      <c r="G65" s="19" t="s">
+      <c r="G65" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="H65" s="18" t="s">
+      <c r="H65" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="I65" s="19" t="s">
+      <c r="I65" s="22" t="s">
         <v>205</v>
       </c>
-      <c r="J65" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K65" s="1">
-        <v>60</v>
-      </c>
-      <c r="L65" s="1">
+      <c r="J65" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K65" s="2">
+        <v>60</v>
+      </c>
+      <c r="L65" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="3:12">
-      <c r="C66" s="3">
+      <c r="C66" s="1">
         <v>61</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E66" s="1">
         <v>11</v>
       </c>
-      <c r="G66" s="17" t="s">
+      <c r="G66" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="H66" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I66" s="19" t="s">
+      <c r="I66" s="22" t="s">
         <v>209</v>
       </c>
-      <c r="J66" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K66" s="3">
-        <v>60</v>
-      </c>
-      <c r="L66" s="3">
+      <c r="J66" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K66" s="1">
+        <v>60</v>
+      </c>
+      <c r="L66" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="3:12">
-      <c r="C67" s="3">
+      <c r="C67" s="1">
         <v>62</v>
       </c>
-      <c r="D67" s="15" t="s">
+      <c r="D67" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="E67" s="3">
+      <c r="E67" s="1">
         <v>11</v>
       </c>
-      <c r="G67" s="17" t="s">
+      <c r="G67" s="20" t="s">
         <v>211</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="H67" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I67" s="19" t="s">
+      <c r="I67" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="J67" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K67" s="3">
-        <v>60</v>
-      </c>
-      <c r="L67" s="3">
+      <c r="J67" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K67" s="1">
+        <v>60</v>
+      </c>
+      <c r="L67" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="3:12">
-      <c r="C68" s="3">
+      <c r="C68" s="1">
         <v>63</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E68" s="1">
         <v>11</v>
       </c>
-      <c r="G68" s="17" t="s">
+      <c r="G68" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I68" s="19" t="s">
+      <c r="I68" s="22" t="s">
         <v>215</v>
       </c>
-      <c r="J68" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K68" s="3">
-        <v>60</v>
-      </c>
-      <c r="L68" s="3">
+      <c r="J68" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K68" s="1">
+        <v>60</v>
+      </c>
+      <c r="L68" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="3:12">
-      <c r="C69" s="3">
+      <c r="C69" s="1">
         <v>64</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E69" s="1">
         <v>11</v>
       </c>
-      <c r="G69" s="17" t="s">
+      <c r="G69" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I69" s="19" t="s">
+      <c r="I69" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="J69" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K69" s="3">
-        <v>60</v>
-      </c>
-      <c r="L69" s="3">
+      <c r="J69" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" s="1">
+        <v>60</v>
+      </c>
+      <c r="L69" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="3:12">
-      <c r="C70" s="3">
+      <c r="C70" s="1">
         <v>65</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E70" s="1">
         <v>11</v>
       </c>
-      <c r="G70" s="17" t="s">
+      <c r="G70" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="H70" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I70" s="19" t="s">
+      <c r="I70" s="22" t="s">
         <v>221</v>
       </c>
-      <c r="J70" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K70" s="3">
-        <v>60</v>
-      </c>
-      <c r="L70" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C71" s="1">
+      <c r="J70" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" s="1">
+        <v>60</v>
+      </c>
+      <c r="L70" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C71" s="2">
         <v>66</v>
       </c>
       <c r="D71" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71" s="2">
         <v>11</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71" s="2">
         <v>11</v>
       </c>
-      <c r="G71" s="19" t="s">
+      <c r="G71" s="22" t="s">
         <v>223</v>
       </c>
-      <c r="H71" s="18" t="s">
+      <c r="H71" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="I71" s="19" t="s">
+      <c r="I71" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="J71" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K71" s="1">
-        <v>60</v>
-      </c>
-      <c r="L71" s="1">
+      <c r="J71" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="K71" s="2">
+        <v>60</v>
+      </c>
+      <c r="L71" s="2">
         <v>60</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:12">
-      <c r="C72" s="3">
+      <c r="C72" s="1">
         <v>67</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="1">
         <v>12</v>
       </c>
-      <c r="G72" s="17" t="s">
+      <c r="G72" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="I72" s="19" t="s">
+      <c r="I72" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="J72" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K72" s="3">
-        <v>60</v>
-      </c>
-      <c r="L72" s="3">
+      <c r="J72" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K72" s="1">
+        <v>60</v>
+      </c>
+      <c r="L72" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="3:12">
-      <c r="C73" s="3">
+      <c r="C73" s="1">
         <v>68</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E73" s="1">
         <v>12</v>
       </c>
-      <c r="G73" s="17" t="s">
+      <c r="G73" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="H73" s="16" t="s">
+      <c r="H73" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="I73" s="19" t="s">
+      <c r="I73" s="22" t="s">
         <v>231</v>
       </c>
-      <c r="J73" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K73" s="3">
-        <v>60</v>
-      </c>
-      <c r="L73" s="3">
+      <c r="J73" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K73" s="1">
+        <v>60</v>
+      </c>
+      <c r="L73" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:12">
-      <c r="C74" s="3">
+      <c r="C74" s="1">
         <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E74" s="1">
         <v>12</v>
       </c>
-      <c r="G74" s="17" t="s">
+      <c r="G74" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="H74" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="I74" s="19" t="s">
+      <c r="I74" s="22" t="s">
         <v>234</v>
       </c>
-      <c r="J74" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K74" s="3">
-        <v>60</v>
-      </c>
-      <c r="L74" s="3">
+      <c r="J74" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K74" s="1">
+        <v>60</v>
+      </c>
+      <c r="L74" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:12">
-      <c r="C75" s="3">
+      <c r="C75" s="1">
         <v>70</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E75" s="1">
         <v>12</v>
       </c>
-      <c r="G75" s="17" t="s">
+      <c r="G75" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="H75" s="16" t="s">
+      <c r="H75" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="I75" s="19" t="s">
+      <c r="I75" s="22" t="s">
         <v>237</v>
       </c>
-      <c r="J75" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K75" s="3">
-        <v>60</v>
-      </c>
-      <c r="L75" s="3">
+      <c r="J75" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K75" s="1">
+        <v>60</v>
+      </c>
+      <c r="L75" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="3:12">
-      <c r="C76" s="3">
+      <c r="C76" s="1">
         <v>71</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E76" s="1">
         <v>12</v>
       </c>
-      <c r="G76" s="17" t="s">
+      <c r="G76" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="H76" s="16" t="s">
+      <c r="H76" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="I76" s="19" t="s">
+      <c r="I76" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="J76" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K76" s="3">
-        <v>60</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="J76" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K76" s="1">
+        <v>60</v>
+      </c>
+      <c r="L76" s="1">
         <v>60</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:12">
-      <c r="C77" s="3">
+      <c r="C77" s="1">
         <v>72</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="E77" s="3">
+      <c r="E77" s="1">
         <v>12</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77" s="1">
         <v>12</v>
       </c>
-      <c r="G77" s="17" t="s">
+      <c r="G77" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="H77" s="16" t="s">
+      <c r="H77" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="I77" s="19" t="s">
+      <c r="I77" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="J77" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="K77" s="1">
-        <v>60</v>
-      </c>
-      <c r="L77" s="1">
+      <c r="J77" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K77" s="2">
+        <v>60</v>
+      </c>
+      <c r="L77" s="2">
         <v>60</v>
       </c>
     </row>
@@ -4097,4 +4197,3013 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A3:N77"/>
+  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
+  <cols>
+    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7272727272727" style="1" customWidth="1"/>
+    <col min="5" max="6" width="11.6272727272727" style="1" customWidth="1"/>
+    <col min="7" max="7" width="33.1818181818182" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.1818181818182" style="1" customWidth="1"/>
+    <col min="9" max="9" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.7272727272727" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.5454545454545" style="1" customWidth="1"/>
+    <col min="12" max="12" width="31.1818181818182" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1818181818182" style="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" customWidth="1"/>
+    <col min="15" max="16382" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="16383" max="16384" width="9.25454545454545" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C6" s="1">
+        <v>73</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1">
+        <v>13</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="1">
+        <v>50</v>
+      </c>
+      <c r="N6" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C7" s="1">
+        <v>74</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="1">
+        <v>13</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="1">
+        <v>50</v>
+      </c>
+      <c r="N7" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C8" s="1">
+        <v>75</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1">
+        <v>13</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L8" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="1">
+        <v>50</v>
+      </c>
+      <c r="N8" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C9" s="1">
+        <v>76</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1">
+        <v>13</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="1">
+        <v>50</v>
+      </c>
+      <c r="N9" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C10" s="1">
+        <v>77</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1">
+        <v>13</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L10" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="1">
+        <v>50</v>
+      </c>
+      <c r="N10" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C11" s="1">
+        <v>78</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="1">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>247</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L11" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="1">
+        <v>50</v>
+      </c>
+      <c r="N11" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C12" s="1">
+        <v>79</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" ref="E12:E75" si="0">E6+1</f>
+        <v>14</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="1">
+        <v>50</v>
+      </c>
+      <c r="N12" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C13" s="1">
+        <v>80</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L13" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="1">
+        <v>50</v>
+      </c>
+      <c r="N13" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C14" s="1">
+        <v>81</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="1">
+        <v>50</v>
+      </c>
+      <c r="N14" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C15" s="1">
+        <v>82</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L15" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="1">
+        <v>50</v>
+      </c>
+      <c r="N15" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C16" s="1">
+        <v>83</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="1">
+        <v>50</v>
+      </c>
+      <c r="N16" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C17" s="1">
+        <v>84</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L17" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="1">
+        <v>50</v>
+      </c>
+      <c r="N17" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C18" s="1">
+        <v>85</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H18" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L18" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" s="1">
+        <v>50</v>
+      </c>
+      <c r="N18" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C19" s="1">
+        <v>86</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H19" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I19" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L19" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" s="1">
+        <v>50</v>
+      </c>
+      <c r="N19" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C20" s="1">
+        <v>87</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="1">
+        <v>50</v>
+      </c>
+      <c r="N20" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C21" s="1">
+        <v>88</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J21" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L21" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" s="1">
+        <v>50</v>
+      </c>
+      <c r="N21" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C22" s="1">
+        <v>89</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J22" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="1">
+        <v>50</v>
+      </c>
+      <c r="N22" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1">
+        <v>90</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="F23" s="2">
+        <v>3</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>257</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J23" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L23" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" s="1">
+        <v>50</v>
+      </c>
+      <c r="N23" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A24" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C24" s="1">
+        <v>91</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L24" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="1">
+        <v>50</v>
+      </c>
+      <c r="N24" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A25" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C25" s="1">
+        <v>92</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L25" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M25" s="1">
+        <v>50</v>
+      </c>
+      <c r="N25" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A26" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="1">
+        <v>93</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H26" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I26" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L26" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="1">
+        <v>50</v>
+      </c>
+      <c r="N26" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A27" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C27" s="1">
+        <v>94</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L27" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="1">
+        <v>50</v>
+      </c>
+      <c r="N27" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A28" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" s="1">
+        <v>95</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L28" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" s="1">
+        <v>50</v>
+      </c>
+      <c r="N28" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A29" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C29" s="1">
+        <v>96</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="F29" s="2">
+        <v>4</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>259</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" s="1">
+        <v>50</v>
+      </c>
+      <c r="N29" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" s="3" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A30" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C30" s="1">
+        <v>97</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" s="1">
+        <v>50</v>
+      </c>
+      <c r="N30" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A31" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C31" s="1">
+        <v>98</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I31" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M31" s="1">
+        <v>50</v>
+      </c>
+      <c r="N31" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C32" s="1">
+        <v>99</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I32" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M32" s="1">
+        <v>50</v>
+      </c>
+      <c r="N32" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A33" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C33" s="1">
+        <v>100</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I33" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M33" s="1">
+        <v>50</v>
+      </c>
+      <c r="N33" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C34" s="1">
+        <v>101</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H34" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L34" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M34" s="1">
+        <v>50</v>
+      </c>
+      <c r="N34" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A35" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="1">
+        <v>102</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="F35" s="2">
+        <v>5</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H35" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I35" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M35" s="1">
+        <v>50</v>
+      </c>
+      <c r="N35" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A36" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C36" s="1">
+        <v>103</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H36" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L36" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M36" s="1">
+        <v>50</v>
+      </c>
+      <c r="N36" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A37" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C37" s="1">
+        <v>104</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L37" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M37" s="1">
+        <v>50</v>
+      </c>
+      <c r="N37" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A38" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C38" s="1">
+        <v>105</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I38" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38" s="1">
+        <v>50</v>
+      </c>
+      <c r="N38" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A39" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C39" s="1">
+        <v>106</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H39" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I39" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L39" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" s="1">
+        <v>50</v>
+      </c>
+      <c r="N39" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C40" s="1">
+        <v>107</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J40" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L40" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M40" s="1">
+        <v>50</v>
+      </c>
+      <c r="N40" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A41" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C41" s="1">
+        <v>108</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="F41" s="2">
+        <v>6</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L41" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M41" s="1">
+        <v>50</v>
+      </c>
+      <c r="N41" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A42" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C42" s="1">
+        <v>109</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="I42" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L42" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M42" s="1">
+        <v>50</v>
+      </c>
+      <c r="N42" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A43" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C43" s="1">
+        <v>110</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L43" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M43" s="1">
+        <v>50</v>
+      </c>
+      <c r="N43" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A44" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44" s="1">
+        <v>111</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E44" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L44" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M44" s="1">
+        <v>50</v>
+      </c>
+      <c r="N44" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A45" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C45" s="1">
+        <v>112</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E45" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L45" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M45" s="1">
+        <v>50</v>
+      </c>
+      <c r="N45" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A46" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C46" s="1">
+        <v>113</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J46" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L46" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M46" s="1">
+        <v>50</v>
+      </c>
+      <c r="N46" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A47" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C47" s="1">
+        <v>114</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E47" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="F47" s="2">
+        <v>7</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H47" s="8"/>
+      <c r="I47" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L47" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M47" s="1">
+        <v>50</v>
+      </c>
+      <c r="N47" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A48" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48" s="1">
+        <v>115</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E48" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K48" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L48" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M48" s="1">
+        <v>50</v>
+      </c>
+      <c r="N48" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A49" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C49" s="1">
+        <v>116</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E49" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L49" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M49" s="1">
+        <v>50</v>
+      </c>
+      <c r="N49" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A50" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C50" s="1">
+        <v>117</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E50" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J50" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L50" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M50" s="1">
+        <v>50</v>
+      </c>
+      <c r="N50" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A51" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51" s="1">
+        <v>118</v>
+      </c>
+      <c r="D51" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J51" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K51" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L51" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M51" s="1">
+        <v>50</v>
+      </c>
+      <c r="N51" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A52" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C52" s="1">
+        <v>119</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E52" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G52" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K52" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L52" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M52" s="1">
+        <v>50</v>
+      </c>
+      <c r="N52" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A53" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C53" s="1">
+        <v>120</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F53" s="2">
+        <v>8</v>
+      </c>
+      <c r="G53" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="H53" s="8"/>
+      <c r="I53" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K53" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L53" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M53" s="1">
+        <v>50</v>
+      </c>
+      <c r="N53" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A54" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54" s="1">
+        <v>121</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="E54" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="I54" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J54" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K54" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L54" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M54" s="1">
+        <v>50</v>
+      </c>
+      <c r="N54" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A55" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C55" s="1">
+        <v>122</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="I55" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J55" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K55" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L55" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M55" s="1">
+        <v>50</v>
+      </c>
+      <c r="N55" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A56" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C56" s="1">
+        <v>123</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E56" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="I56" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K56" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L56" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M56" s="1">
+        <v>50</v>
+      </c>
+      <c r="N56" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A57" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C57" s="1">
+        <v>124</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="E57" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="I57" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L57" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M57" s="1">
+        <v>50</v>
+      </c>
+      <c r="N57" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C58" s="1">
+        <v>125</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E58" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="I58" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K58" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L58" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="M58" s="1">
+        <v>50</v>
+      </c>
+      <c r="N58" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A59" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C59" s="1">
+        <v>126</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="F59" s="2">
+        <v>9</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J59" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K59" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L59" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M59" s="1">
+        <v>50</v>
+      </c>
+      <c r="N59" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A60" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C60" s="1">
+        <v>127</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E60" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J60" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K60" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L60" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M60" s="1">
+        <v>50</v>
+      </c>
+      <c r="N60" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A61" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C61" s="1">
+        <v>128</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="E61" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J61" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K61" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L61" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M61" s="1">
+        <v>50</v>
+      </c>
+      <c r="N61" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A62" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C62" s="1">
+        <v>129</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="E62" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J62" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K62" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L62" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M62" s="1">
+        <v>50</v>
+      </c>
+      <c r="N62" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A63" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C63" s="1">
+        <v>130</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E63" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K63" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L63" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M63" s="1">
+        <v>50</v>
+      </c>
+      <c r="N63" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A64" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C64" s="1">
+        <v>131</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E64" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="I64" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J64" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K64" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L64" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M64" s="1">
+        <v>50</v>
+      </c>
+      <c r="N64" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A65" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C65" s="1">
+        <v>132</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="E65" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="F65" s="2">
+        <v>10</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="I65" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J65" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K65" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L65" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M65" s="1">
+        <v>50</v>
+      </c>
+      <c r="N65" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A66" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C66" s="1">
+        <v>133</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="E66" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J66" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K66" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L66" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M66" s="1">
+        <v>50</v>
+      </c>
+      <c r="N66" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A67" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C67" s="1">
+        <v>134</v>
+      </c>
+      <c r="D67" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="E67" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J67" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K67" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L67" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M67" s="1">
+        <v>50</v>
+      </c>
+      <c r="N67" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68" s="1">
+        <v>135</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="E68" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="G68" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J68" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K68" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L68" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M68" s="1">
+        <v>50</v>
+      </c>
+      <c r="N68" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A69" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C69" s="1">
+        <v>136</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="E69" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="G69" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="H69" s="17"/>
+      <c r="I69" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J69" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K69" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L69" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M69" s="1">
+        <v>50</v>
+      </c>
+      <c r="N69" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A70" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C70" s="1">
+        <v>137</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="E70" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="G70" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J70" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K70" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L70" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M70" s="1">
+        <v>50</v>
+      </c>
+      <c r="N70" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A71" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C71" s="1">
+        <v>138</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E71" s="1">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="F71" s="2">
+        <v>11</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="I71" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J71" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K71" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L71" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="M71" s="1">
+        <v>50</v>
+      </c>
+      <c r="N71" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A72" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C72" s="1">
+        <v>139</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E72" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G72" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="I72" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J72" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K72" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L72" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M72" s="1">
+        <v>50</v>
+      </c>
+      <c r="N72" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A73" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C73" s="1">
+        <v>140</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E73" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G73" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="I73" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J73" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K73" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L73" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M73" s="1">
+        <v>50</v>
+      </c>
+      <c r="N73" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A74" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" s="1">
+        <v>141</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E74" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G74" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="I74" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J74" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K74" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L74" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M74" s="1">
+        <v>50</v>
+      </c>
+      <c r="N74" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A75" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C75" s="1">
+        <v>142</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="G75" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K75" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L75" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M75" s="1">
+        <v>50</v>
+      </c>
+      <c r="N75" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A76" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C76" s="1">
+        <v>143</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E76" s="1">
+        <f>E70+1</f>
+        <v>24</v>
+      </c>
+      <c r="G76" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="I76" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J76" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K76" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L76" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="M76" s="1">
+        <v>50</v>
+      </c>
+      <c r="N76" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A77" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C77" s="1">
+        <v>144</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E77" s="1">
+        <f>E71+1</f>
+        <v>24</v>
+      </c>
+      <c r="F77" s="1">
+        <v>12</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="I77" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="J77" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="K77" s="20" t="s">
+        <v>250</v>
+      </c>
+      <c r="L77" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M77" s="1">
+        <v>50</v>
+      </c>
+      <c r="N77" s="1">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C3:C1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C1048576" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="267">
   <si>
     <t>_Id</t>
   </si>
@@ -849,9 +849,6 @@
     <t>30001,180073</t>
   </si>
   <si>
-    <t>1,0</t>
-  </si>
-  <si>
     <t>2074,4007,5013,3004</t>
   </si>
   <si>
@@ -886,6 +883,21 @@
   </si>
   <si>
     <t>7,0,0,0</t>
+  </si>
+  <si>
+    <t>8,0,0,0</t>
+  </si>
+  <si>
+    <t>9,0,0,0</t>
+  </si>
+  <si>
+    <t>10,0,0,0</t>
+  </si>
+  <si>
+    <t>11,0,0,0</t>
+  </si>
+  <si>
+    <t>12,0,0,0</t>
   </si>
 </sst>
 </file>
@@ -1546,7 +1558,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1580,8 +1592,6 @@
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
@@ -1589,7 +1599,6 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2068,16 +2077,16 @@
       <c r="E6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="J6" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="1">
@@ -2097,16 +2106,16 @@
       <c r="E7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="1">
@@ -2126,16 +2135,16 @@
       <c r="E8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="19" t="s">
+      <c r="H8" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="19" t="s">
+      <c r="J8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="1">
@@ -2155,16 +2164,16 @@
       <c r="E9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="1">
@@ -2184,16 +2193,16 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="1">
@@ -2216,16 +2225,16 @@
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="1">
@@ -2245,16 +2254,16 @@
       <c r="E12" s="1">
         <v>2</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="19" t="s">
+      <c r="H12" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="J12" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="1">
@@ -2274,16 +2283,16 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G13" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="J13" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="1">
@@ -2303,16 +2312,16 @@
       <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="19" t="s">
+      <c r="J14" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="1">
@@ -2332,16 +2341,16 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="1">
@@ -2361,16 +2370,16 @@
       <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="H16" s="19" t="s">
+      <c r="H16" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="19" t="s">
+      <c r="I16" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="1">
@@ -2393,16 +2402,16 @@
       <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="19" t="s">
+      <c r="J17" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="1">
@@ -2422,16 +2431,16 @@
       <c r="E18" s="1">
         <v>3</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="19" t="s">
+      <c r="H18" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="19" t="s">
+      <c r="J18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="1">
@@ -2451,16 +2460,16 @@
       <c r="E19" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="J19" s="19" t="s">
+      <c r="I19" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="J19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K19" s="1">
@@ -2480,16 +2489,16 @@
       <c r="E20" s="1">
         <v>3</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="H20" s="19" t="s">
+      <c r="H20" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="J20" s="19" t="s">
+      <c r="J20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="1">
@@ -2509,16 +2518,16 @@
       <c r="E21" s="1">
         <v>3</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="J21" s="19" t="s">
+      <c r="J21" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K21" s="1">
@@ -2538,16 +2547,16 @@
       <c r="E22" s="1">
         <v>3</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="19" t="s">
+      <c r="H22" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="1">
@@ -2570,16 +2579,16 @@
       <c r="F23" s="2">
         <v>3</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="G23" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="I23" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="J23" s="19" t="s">
+      <c r="J23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="1">
@@ -2599,16 +2608,16 @@
       <c r="E24" s="3">
         <v>4</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G24" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="I24" s="24" t="s">
+      <c r="I24" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="J24" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K24" s="1">
@@ -2628,16 +2637,16 @@
       <c r="E25" s="1">
         <v>4</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="H25" s="23" t="s">
+      <c r="H25" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="20" t="s">
+      <c r="I25" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="J25" s="19" t="s">
+      <c r="J25" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K25" s="1">
@@ -2657,16 +2666,16 @@
       <c r="E26" s="1">
         <v>4</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="20" t="s">
+      <c r="I26" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="J26" s="19" t="s">
+      <c r="J26" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K26" s="1">
@@ -2686,16 +2695,16 @@
       <c r="E27" s="1">
         <v>4</v>
       </c>
-      <c r="G27" s="19" t="s">
+      <c r="G27" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="I27" s="20" t="s">
+      <c r="I27" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="J27" s="19" t="s">
+      <c r="J27" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="1">
@@ -2715,16 +2724,16 @@
       <c r="E28" s="1">
         <v>4</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H28" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="I28" s="20" t="s">
+      <c r="I28" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="J28" s="19" t="s">
+      <c r="J28" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="1">
@@ -2747,16 +2756,16 @@
       <c r="F29" s="2">
         <v>4</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="G29" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="H29" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="I29" s="22" t="s">
+      <c r="I29" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="J29" s="19" t="s">
+      <c r="J29" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="1">
@@ -2776,16 +2785,16 @@
       <c r="E30" s="3">
         <v>5</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I30" s="24" t="s">
+      <c r="I30" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="J30" s="19" t="s">
+      <c r="J30" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K30" s="1">
@@ -2805,16 +2814,16 @@
       <c r="E31" s="1">
         <v>5</v>
       </c>
-      <c r="G31" s="19" t="s">
+      <c r="G31" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="H31" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="I31" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="J31" s="19" t="s">
+      <c r="J31" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K31" s="1">
@@ -2834,16 +2843,16 @@
       <c r="E32" s="1">
         <v>5</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="G32" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I32" s="20" t="s">
+      <c r="I32" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="J32" s="19" t="s">
+      <c r="J32" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K32" s="1">
@@ -2863,16 +2872,16 @@
       <c r="E33" s="1">
         <v>5</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="G33" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="23" t="s">
+      <c r="H33" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="19" t="s">
+      <c r="J33" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="1">
@@ -2892,16 +2901,16 @@
       <c r="E34" s="1">
         <v>5</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="G34" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I34" s="20" t="s">
+      <c r="I34" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="J34" s="19" t="s">
+      <c r="J34" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="1">
@@ -2924,16 +2933,16 @@
       <c r="F35" s="2">
         <v>5</v>
       </c>
-      <c r="G35" s="21" t="s">
+      <c r="G35" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="H35" s="23" t="s">
+      <c r="H35" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="I35" s="22" t="s">
+      <c r="I35" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J35" s="19" t="s">
+      <c r="J35" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="1">
@@ -2953,16 +2962,16 @@
       <c r="E36" s="1">
         <v>6</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="H36" s="19" t="s">
+      <c r="H36" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="I36" s="20" t="s">
+      <c r="I36" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="J36" s="19" t="s">
+      <c r="J36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K36" s="1">
@@ -2982,16 +2991,16 @@
       <c r="E37" s="1">
         <v>6</v>
       </c>
-      <c r="G37" s="19" t="s">
+      <c r="G37" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="J37" s="19" t="s">
+      <c r="J37" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="1">
@@ -3011,16 +3020,16 @@
       <c r="E38" s="1">
         <v>6</v>
       </c>
-      <c r="G38" s="19" t="s">
+      <c r="G38" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="H38" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="I38" s="20" t="s">
+      <c r="I38" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="J38" s="19" t="s">
+      <c r="J38" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="1">
@@ -3040,16 +3049,16 @@
       <c r="E39" s="1">
         <v>6</v>
       </c>
-      <c r="G39" s="19" t="s">
+      <c r="G39" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="H39" s="19" t="s">
+      <c r="H39" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="20" t="s">
+      <c r="I39" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="J39" s="19" t="s">
+      <c r="J39" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="1">
@@ -3069,16 +3078,16 @@
       <c r="E40" s="1">
         <v>6</v>
       </c>
-      <c r="G40" s="19" t="s">
+      <c r="G40" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="H40" s="19" t="s">
+      <c r="H40" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="I40" s="20" t="s">
+      <c r="I40" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="J40" s="19" t="s">
+      <c r="J40" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="1">
@@ -3101,16 +3110,16 @@
       <c r="F41" s="2">
         <v>6</v>
       </c>
-      <c r="G41" s="21" t="s">
+      <c r="G41" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="H41" s="19" t="s">
+      <c r="H41" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="I41" s="22" t="s">
+      <c r="I41" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="J41" s="19" t="s">
+      <c r="J41" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="1">
@@ -3130,16 +3139,16 @@
       <c r="E42" s="1">
         <v>7</v>
       </c>
-      <c r="G42" s="19" t="s">
+      <c r="G42" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="H42" s="19" t="s">
+      <c r="H42" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="I42" s="24" t="s">
+      <c r="I42" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="J42" s="19" t="s">
+      <c r="J42" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="1">
@@ -3159,16 +3168,16 @@
       <c r="E43" s="1">
         <v>7</v>
       </c>
-      <c r="G43" s="19" t="s">
+      <c r="G43" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="H43" s="19" t="s">
+      <c r="H43" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="I43" s="24" t="s">
+      <c r="I43" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="J43" s="19" t="s">
+      <c r="J43" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K43" s="1">
@@ -3188,16 +3197,16 @@
       <c r="E44" s="1">
         <v>7</v>
       </c>
-      <c r="G44" s="19" t="s">
+      <c r="G44" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="H44" s="19" t="s">
+      <c r="H44" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="I44" s="24" t="s">
+      <c r="I44" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="J44" s="19" t="s">
+      <c r="J44" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K44" s="1">
@@ -3217,16 +3226,16 @@
       <c r="E45" s="1">
         <v>7</v>
       </c>
-      <c r="G45" s="19" t="s">
+      <c r="G45" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="H45" s="19" t="s">
+      <c r="H45" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="I45" s="24" t="s">
+      <c r="I45" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="J45" s="19" t="s">
+      <c r="J45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="1">
@@ -3247,16 +3256,16 @@
         <v>7</v>
       </c>
       <c r="F46" s="1"/>
-      <c r="G46" s="19" t="s">
+      <c r="G46" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="H46" s="19" t="s">
+      <c r="H46" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="I46" s="24" t="s">
+      <c r="I46" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="J46" s="19" t="s">
+      <c r="J46" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K46" s="1">
@@ -3279,16 +3288,16 @@
       <c r="F47" s="2">
         <v>7</v>
       </c>
-      <c r="G47" s="21" t="s">
+      <c r="G47" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="H47" s="21" t="s">
+      <c r="H47" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="I47" s="22" t="s">
+      <c r="I47" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="J47" s="21" t="s">
+      <c r="J47" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="2">
@@ -3308,16 +3317,16 @@
       <c r="E48" s="1">
         <v>8</v>
       </c>
-      <c r="G48" s="19" t="s">
+      <c r="G48" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="H48" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="I48" s="24" t="s">
+      <c r="I48" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="J48" s="19" t="s">
+      <c r="J48" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K48" s="1">
@@ -3337,16 +3346,16 @@
       <c r="E49" s="1">
         <v>8</v>
       </c>
-      <c r="G49" s="19" t="s">
+      <c r="G49" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="H49" s="19" t="s">
+      <c r="H49" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="I49" s="24" t="s">
+      <c r="I49" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="J49" s="19" t="s">
+      <c r="J49" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="1">
@@ -3366,16 +3375,16 @@
       <c r="E50" s="1">
         <v>8</v>
       </c>
-      <c r="G50" s="19" t="s">
+      <c r="G50" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="H50" s="19" t="s">
+      <c r="H50" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="I50" s="24" t="s">
+      <c r="I50" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="J50" s="19" t="s">
+      <c r="J50" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="1">
@@ -3395,16 +3404,16 @@
       <c r="E51" s="1">
         <v>8</v>
       </c>
-      <c r="G51" s="19" t="s">
+      <c r="G51" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="H51" s="19" t="s">
+      <c r="H51" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="I51" s="24" t="s">
+      <c r="I51" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="J51" s="19" t="s">
+      <c r="J51" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K51" s="1">
@@ -3424,16 +3433,16 @@
       <c r="E52" s="1">
         <v>8</v>
       </c>
-      <c r="G52" s="19" t="s">
+      <c r="G52" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="19" t="s">
+      <c r="H52" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="I52" s="24" t="s">
+      <c r="I52" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="J52" s="19" t="s">
+      <c r="J52" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K52" s="1">
@@ -3456,16 +3465,16 @@
       <c r="F53" s="2">
         <v>8</v>
       </c>
-      <c r="G53" s="21" t="s">
+      <c r="G53" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="H53" s="21" t="s">
+      <c r="H53" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="I53" s="22" t="s">
+      <c r="I53" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="J53" s="21" t="s">
+      <c r="J53" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K53" s="2">
@@ -3485,16 +3494,16 @@
       <c r="E54" s="1">
         <v>9</v>
       </c>
-      <c r="G54" s="20" t="s">
+      <c r="G54" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="H54" s="19" t="s">
+      <c r="H54" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="I54" s="22" t="s">
+      <c r="I54" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="J54" s="19" t="s">
+      <c r="J54" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K54" s="1">
@@ -3514,16 +3523,16 @@
       <c r="E55" s="1">
         <v>9</v>
       </c>
-      <c r="G55" s="20" t="s">
+      <c r="G55" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H55" s="19" t="s">
+      <c r="H55" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="I55" s="22" t="s">
+      <c r="I55" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="J55" s="19" t="s">
+      <c r="J55" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K55" s="1">
@@ -3543,16 +3552,16 @@
       <c r="E56" s="1">
         <v>9</v>
       </c>
-      <c r="G56" s="20" t="s">
+      <c r="G56" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="H56" s="19" t="s">
+      <c r="H56" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="I56" s="22" t="s">
+      <c r="I56" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="J56" s="19" t="s">
+      <c r="J56" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K56" s="1">
@@ -3572,16 +3581,16 @@
       <c r="E57" s="1">
         <v>9</v>
       </c>
-      <c r="G57" s="20" t="s">
+      <c r="G57" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="H57" s="19" t="s">
+      <c r="H57" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="I57" s="22" t="s">
+      <c r="I57" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="J57" s="19" t="s">
+      <c r="J57" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K57" s="1">
@@ -3601,16 +3610,16 @@
       <c r="E58" s="1">
         <v>9</v>
       </c>
-      <c r="G58" s="20" t="s">
+      <c r="G58" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="H58" s="19" t="s">
+      <c r="H58" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="I58" s="22" t="s">
+      <c r="I58" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="J58" s="19" t="s">
+      <c r="J58" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K58" s="1">
@@ -3633,16 +3642,16 @@
       <c r="F59" s="2">
         <v>9</v>
       </c>
-      <c r="G59" s="22" t="s">
+      <c r="G59" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="H59" s="21" t="s">
+      <c r="H59" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="I59" s="22" t="s">
+      <c r="I59" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="J59" s="21" t="s">
+      <c r="J59" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K59" s="2">
@@ -3662,16 +3671,16 @@
       <c r="E60" s="1">
         <v>10</v>
       </c>
-      <c r="G60" s="20" t="s">
+      <c r="G60" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="H60" s="19" t="s">
+      <c r="H60" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="I60" s="22" t="s">
+      <c r="I60" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="J60" s="19" t="s">
+      <c r="J60" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K60" s="1">
@@ -3691,16 +3700,16 @@
       <c r="E61" s="1">
         <v>10</v>
       </c>
-      <c r="G61" s="20" t="s">
+      <c r="G61" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="H61" s="19" t="s">
+      <c r="H61" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="I61" s="22" t="s">
+      <c r="I61" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="J61" s="19" t="s">
+      <c r="J61" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K61" s="1">
@@ -3720,16 +3729,16 @@
       <c r="E62" s="1">
         <v>10</v>
       </c>
-      <c r="G62" s="20" t="s">
+      <c r="G62" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="H62" s="19" t="s">
+      <c r="H62" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="I62" s="22" t="s">
+      <c r="I62" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="J62" s="19" t="s">
+      <c r="J62" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K62" s="1">
@@ -3749,16 +3758,16 @@
       <c r="E63" s="1">
         <v>10</v>
       </c>
-      <c r="G63" s="20" t="s">
+      <c r="G63" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="H63" s="19" t="s">
+      <c r="H63" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="I63" s="22" t="s">
+      <c r="I63" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="J63" s="19" t="s">
+      <c r="J63" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K63" s="1">
@@ -3778,16 +3787,16 @@
       <c r="E64" s="1">
         <v>10</v>
       </c>
-      <c r="G64" s="20" t="s">
+      <c r="G64" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="H64" s="19" t="s">
+      <c r="H64" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="I64" s="22" t="s">
+      <c r="I64" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="J64" s="19" t="s">
+      <c r="J64" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K64" s="1">
@@ -3810,16 +3819,16 @@
       <c r="F65" s="2">
         <v>10</v>
       </c>
-      <c r="G65" s="22" t="s">
+      <c r="G65" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="H65" s="21" t="s">
+      <c r="H65" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="I65" s="22" t="s">
+      <c r="I65" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="J65" s="21" t="s">
+      <c r="J65" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K65" s="2">
@@ -3839,16 +3848,16 @@
       <c r="E66" s="1">
         <v>11</v>
       </c>
-      <c r="G66" s="20" t="s">
+      <c r="G66" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="H66" s="19" t="s">
+      <c r="H66" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="I66" s="22" t="s">
+      <c r="I66" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="J66" s="19" t="s">
+      <c r="J66" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K66" s="1">
@@ -3868,16 +3877,16 @@
       <c r="E67" s="1">
         <v>11</v>
       </c>
-      <c r="G67" s="20" t="s">
+      <c r="G67" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="H67" s="19" t="s">
+      <c r="H67" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="I67" s="22" t="s">
+      <c r="I67" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="J67" s="19" t="s">
+      <c r="J67" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K67" s="1">
@@ -3897,16 +3906,16 @@
       <c r="E68" s="1">
         <v>11</v>
       </c>
-      <c r="G68" s="20" t="s">
+      <c r="G68" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="H68" s="19" t="s">
+      <c r="H68" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="I68" s="22" t="s">
+      <c r="I68" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="J68" s="19" t="s">
+      <c r="J68" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K68" s="1">
@@ -3926,16 +3935,16 @@
       <c r="E69" s="1">
         <v>11</v>
       </c>
-      <c r="G69" s="20" t="s">
+      <c r="G69" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="H69" s="19" t="s">
+      <c r="H69" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="I69" s="22" t="s">
+      <c r="I69" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="J69" s="19" t="s">
+      <c r="J69" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K69" s="1">
@@ -3955,16 +3964,16 @@
       <c r="E70" s="1">
         <v>11</v>
       </c>
-      <c r="G70" s="20" t="s">
+      <c r="G70" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="H70" s="19" t="s">
+      <c r="H70" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="I70" s="22" t="s">
+      <c r="I70" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="J70" s="19" t="s">
+      <c r="J70" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K70" s="1">
@@ -3987,16 +3996,16 @@
       <c r="F71" s="2">
         <v>11</v>
       </c>
-      <c r="G71" s="22" t="s">
+      <c r="G71" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="H71" s="21" t="s">
+      <c r="H71" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="I71" s="22" t="s">
+      <c r="I71" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="J71" s="21" t="s">
+      <c r="J71" s="19" t="s">
         <v>19</v>
       </c>
       <c r="K71" s="2">
@@ -4016,16 +4025,16 @@
       <c r="E72" s="1">
         <v>12</v>
       </c>
-      <c r="G72" s="20" t="s">
+      <c r="G72" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="H72" s="19" t="s">
+      <c r="H72" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="I72" s="22" t="s">
+      <c r="I72" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="J72" s="19" t="s">
+      <c r="J72" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K72" s="1">
@@ -4045,16 +4054,16 @@
       <c r="E73" s="1">
         <v>12</v>
       </c>
-      <c r="G73" s="20" t="s">
+      <c r="G73" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="H73" s="19" t="s">
+      <c r="H73" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="I73" s="22" t="s">
+      <c r="I73" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="J73" s="19" t="s">
+      <c r="J73" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K73" s="1">
@@ -4074,16 +4083,16 @@
       <c r="E74" s="1">
         <v>12</v>
       </c>
-      <c r="G74" s="20" t="s">
+      <c r="G74" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="H74" s="19" t="s">
+      <c r="H74" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="I74" s="22" t="s">
+      <c r="I74" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="J74" s="19" t="s">
+      <c r="J74" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K74" s="1">
@@ -4103,16 +4112,16 @@
       <c r="E75" s="1">
         <v>12</v>
       </c>
-      <c r="G75" s="20" t="s">
+      <c r="G75" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="H75" s="19" t="s">
+      <c r="H75" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="I75" s="22" t="s">
+      <c r="I75" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="J75" s="19" t="s">
+      <c r="J75" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K75" s="1">
@@ -4132,16 +4141,16 @@
       <c r="E76" s="1">
         <v>12</v>
       </c>
-      <c r="G76" s="20" t="s">
+      <c r="G76" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="H76" s="19" t="s">
+      <c r="H76" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="I76" s="22" t="s">
+      <c r="I76" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="J76" s="19" t="s">
+      <c r="J76" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K76" s="1">
@@ -4164,16 +4173,16 @@
       <c r="F77" s="1">
         <v>12</v>
       </c>
-      <c r="G77" s="20" t="s">
+      <c r="G77" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="H77" s="19" t="s">
+      <c r="H77" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="I77" s="22" t="s">
+      <c r="I77" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="J77" s="19" t="s">
+      <c r="J77" s="17" t="s">
         <v>19</v>
       </c>
       <c r="K77" s="2">
@@ -4344,22 +4353,20 @@
       <c r="E6" s="1">
         <v>13</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="I6" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K6" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L6" s="19" t="s">
+      <c r="K6" s="1"/>
+      <c r="L6" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M6" s="1">
@@ -4379,22 +4386,20 @@
       <c r="E7" s="1">
         <v>13</v>
       </c>
-      <c r="G7" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H7" s="19" t="s">
+      <c r="G7" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H7" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K7" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L7" s="19" t="s">
+      <c r="K7" s="1"/>
+      <c r="L7" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="1">
@@ -4414,22 +4419,20 @@
       <c r="E8" s="1">
         <v>13</v>
       </c>
-      <c r="G8" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H8" s="19" t="s">
+      <c r="G8" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H8" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I8" s="19" t="s">
+      <c r="I8" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K8" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L8" s="19" t="s">
+      <c r="K8" s="1"/>
+      <c r="L8" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M8" s="1">
@@ -4449,22 +4452,20 @@
       <c r="E9" s="1">
         <v>13</v>
       </c>
-      <c r="G9" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H9" s="19" t="s">
+      <c r="G9" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H9" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K9" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L9" s="19" t="s">
+      <c r="K9" s="1"/>
+      <c r="L9" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M9" s="1">
@@ -4484,22 +4485,20 @@
       <c r="E10" s="1">
         <v>13</v>
       </c>
-      <c r="G10" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H10" s="19" t="s">
+      <c r="G10" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H10" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K10" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L10" s="19" t="s">
+      <c r="K10" s="1"/>
+      <c r="L10" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M10" s="1">
@@ -4522,22 +4521,20 @@
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="H11" s="19" t="s">
+      <c r="G11" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K11" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L11" s="19" t="s">
+      <c r="K11" s="1"/>
+      <c r="L11" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M11" s="1">
@@ -4558,22 +4555,20 @@
         <f t="shared" ref="E12:E75" si="0">E6+1</f>
         <v>14</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I12" s="19" t="s">
+      <c r="H12" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="I12" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K12" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L12" s="19" t="s">
+      <c r="K12" s="1"/>
+      <c r="L12" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M12" s="1">
@@ -4594,22 +4589,20 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="G13" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I13" s="19" t="s">
+      <c r="G13" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="I13" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K13" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L13" s="19" t="s">
+      <c r="K13" s="1"/>
+      <c r="L13" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M13" s="1">
@@ -4630,22 +4623,20 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="G14" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I14" s="19" t="s">
+      <c r="G14" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="I14" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J14" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K14" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L14" s="19" t="s">
+      <c r="K14" s="1"/>
+      <c r="L14" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M14" s="1">
@@ -4666,22 +4657,20 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="G15" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I15" s="19" t="s">
+      <c r="G15" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="I15" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K15" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L15" s="19" t="s">
+      <c r="K15" s="1"/>
+      <c r="L15" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M15" s="1">
@@ -4702,22 +4691,20 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="G16" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I16" s="19" t="s">
+      <c r="G16" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="I16" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J16" s="20" t="s">
+      <c r="J16" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K16" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L16" s="19" t="s">
+      <c r="K16" s="1"/>
+      <c r="L16" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M16" s="1">
@@ -4741,22 +4728,20 @@
       <c r="F17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="G17" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H17" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="H17" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K17" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L17" s="19" t="s">
+      <c r="K17" s="1"/>
+      <c r="L17" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M17" s="1">
@@ -4777,22 +4762,20 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G18" s="19" t="s">
+      <c r="G18" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H18" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I18" s="19" t="s">
+      <c r="H18" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="I18" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J18" s="20" t="s">
+      <c r="J18" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K18" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L18" s="19" t="s">
+      <c r="K18" s="1"/>
+      <c r="L18" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M18" s="1">
@@ -4813,22 +4796,20 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G19" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H19" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I19" s="19" t="s">
+      <c r="G19" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="I19" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J19" s="20" t="s">
+      <c r="J19" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K19" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L19" s="19" t="s">
+      <c r="K19" s="1"/>
+      <c r="L19" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M19" s="1">
@@ -4849,22 +4830,20 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G20" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I20" s="19" t="s">
+      <c r="G20" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="I20" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K20" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L20" s="19" t="s">
+      <c r="K20" s="1"/>
+      <c r="L20" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M20" s="1">
@@ -4885,22 +4864,20 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G21" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I21" s="19" t="s">
+      <c r="G21" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="I21" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K21" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L21" s="19" t="s">
+      <c r="K21" s="1"/>
+      <c r="L21" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M21" s="1">
@@ -4921,22 +4898,20 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G22" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I22" s="19" t="s">
+      <c r="G22" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="I22" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J22" s="20" t="s">
+      <c r="J22" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K22" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L22" s="19" t="s">
+      <c r="K22" s="1"/>
+      <c r="L22" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M22" s="1">
@@ -4962,22 +4937,20 @@
       <c r="F23" s="2">
         <v>3</v>
       </c>
-      <c r="G23" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I23" s="19" t="s">
+      <c r="G23" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H23" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="I23" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K23" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L23" s="19" t="s">
+      <c r="K23" s="1"/>
+      <c r="L23" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M23" s="1">
@@ -4989,10 +4962,10 @@
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:14">
       <c r="A24" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C24" s="1">
         <v>91</v>
@@ -5004,22 +4977,20 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H24" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I24" s="19" t="s">
+      <c r="H24" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I24" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K24" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L24" s="19" t="s">
+      <c r="K24" s="1"/>
+      <c r="L24" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M24" s="1">
@@ -5031,10 +5002,10 @@
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A25" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C25" s="1">
         <v>92</v>
@@ -5046,22 +5017,20 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G25" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I25" s="19" t="s">
+      <c r="G25" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I25" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J25" s="20" t="s">
+      <c r="J25" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K25" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L25" s="19" t="s">
+      <c r="K25" s="1"/>
+      <c r="L25" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M25" s="1">
@@ -5073,10 +5042,10 @@
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A26" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C26" s="1">
         <v>93</v>
@@ -5088,22 +5057,20 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G26" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H26" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I26" s="19" t="s">
+      <c r="G26" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I26" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J26" s="20" t="s">
+      <c r="J26" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K26" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L26" s="19" t="s">
+      <c r="K26" s="1"/>
+      <c r="L26" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M26" s="1">
@@ -5115,10 +5082,10 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A27" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C27" s="1">
         <v>94</v>
@@ -5130,22 +5097,20 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G27" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I27" s="19" t="s">
+      <c r="G27" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I27" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J27" s="20" t="s">
+      <c r="J27" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K27" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L27" s="19" t="s">
+      <c r="K27" s="1"/>
+      <c r="L27" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M27" s="1">
@@ -5157,10 +5122,10 @@
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A28" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C28" s="1">
         <v>95</v>
@@ -5172,22 +5137,20 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G28" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H28" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I28" s="19" t="s">
+      <c r="G28" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H28" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I28" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J28" s="20" t="s">
+      <c r="J28" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K28" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L28" s="19" t="s">
+      <c r="K28" s="1"/>
+      <c r="L28" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M28" s="1">
@@ -5199,10 +5162,10 @@
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A29" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C29" s="1">
         <v>96</v>
@@ -5217,22 +5180,20 @@
       <c r="F29" s="2">
         <v>4</v>
       </c>
-      <c r="G29" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>259</v>
-      </c>
-      <c r="I29" s="19" t="s">
+      <c r="G29" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="I29" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J29" s="20" t="s">
+      <c r="J29" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K29" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L29" s="19" t="s">
+      <c r="K29" s="1"/>
+      <c r="L29" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M29" s="1">
@@ -5244,10 +5205,10 @@
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C30" s="1">
         <v>97</v>
@@ -5259,22 +5220,20 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H30" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="I30" s="19" t="s">
+      <c r="H30" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I30" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J30" s="20" t="s">
+      <c r="J30" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K30" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L30" s="19" t="s">
+      <c r="K30" s="1"/>
+      <c r="L30" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M30" s="1">
@@ -5286,10 +5245,10 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A31" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C31" s="1">
         <v>98</v>
@@ -5301,22 +5260,20 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="G31" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H31" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="I31" s="19" t="s">
+      <c r="G31" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I31" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J31" s="20" t="s">
+      <c r="J31" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K31" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L31" s="19" t="s">
+      <c r="K31" s="1"/>
+      <c r="L31" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M31" s="1">
@@ -5328,10 +5285,10 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A32" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C32" s="1">
         <v>99</v>
@@ -5343,22 +5300,20 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="G32" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H32" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="I32" s="19" t="s">
+      <c r="G32" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I32" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J32" s="20" t="s">
+      <c r="J32" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K32" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L32" s="19" t="s">
+      <c r="K32" s="1"/>
+      <c r="L32" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M32" s="1">
@@ -5370,10 +5325,10 @@
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A33" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C33" s="1">
         <v>100</v>
@@ -5385,22 +5340,20 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="G33" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="I33" s="19" t="s">
+      <c r="G33" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I33" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J33" s="20" t="s">
+      <c r="J33" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K33" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L33" s="19" t="s">
+      <c r="K33" s="1"/>
+      <c r="L33" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M33" s="1">
@@ -5412,10 +5365,10 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C34" s="1">
         <v>101</v>
@@ -5427,22 +5380,20 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="G34" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="I34" s="19" t="s">
+      <c r="G34" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I34" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J34" s="20" t="s">
+      <c r="J34" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K34" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L34" s="19" t="s">
+      <c r="K34" s="1"/>
+      <c r="L34" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M34" s="1">
@@ -5454,10 +5405,10 @@
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A35" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C35" s="1">
         <v>102</v>
@@ -5472,22 +5423,20 @@
       <c r="F35" s="2">
         <v>5</v>
       </c>
-      <c r="G35" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="H35" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="I35" s="19" t="s">
+      <c r="G35" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>259</v>
+      </c>
+      <c r="I35" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J35" s="20" t="s">
+      <c r="J35" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K35" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L35" s="19" t="s">
+      <c r="K35" s="1"/>
+      <c r="L35" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M35" s="1">
@@ -5499,10 +5448,10 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A36" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C36" s="1">
         <v>103</v>
@@ -5514,22 +5463,20 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="G36" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H36" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="I36" s="19" t="s">
+      <c r="H36" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="I36" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J36" s="20" t="s">
+      <c r="J36" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K36" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L36" s="19" t="s">
+      <c r="K36" s="1"/>
+      <c r="L36" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M36" s="1">
@@ -5541,10 +5488,10 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A37" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C37" s="1">
         <v>104</v>
@@ -5556,22 +5503,20 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G37" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H37" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="I37" s="19" t="s">
+      <c r="G37" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="I37" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J37" s="20" t="s">
+      <c r="J37" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K37" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L37" s="19" t="s">
+      <c r="K37" s="1"/>
+      <c r="L37" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M37" s="1">
@@ -5583,10 +5528,10 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A38" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C38" s="1">
         <v>105</v>
@@ -5598,22 +5543,20 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G38" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H38" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="I38" s="19" t="s">
+      <c r="G38" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="I38" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J38" s="20" t="s">
+      <c r="J38" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K38" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L38" s="19" t="s">
+      <c r="K38" s="1"/>
+      <c r="L38" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M38" s="1">
@@ -5625,10 +5568,10 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A39" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C39" s="1">
         <v>106</v>
@@ -5640,22 +5583,20 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G39" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H39" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="I39" s="19" t="s">
+      <c r="G39" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="I39" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J39" s="20" t="s">
+      <c r="J39" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K39" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L39" s="19" t="s">
+      <c r="K39" s="1"/>
+      <c r="L39" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M39" s="1">
@@ -5667,10 +5608,10 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A40" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C40" s="1">
         <v>107</v>
@@ -5682,22 +5623,20 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="G40" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="I40" s="19" t="s">
+      <c r="G40" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="I40" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J40" s="20" t="s">
+      <c r="J40" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K40" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L40" s="19" t="s">
+      <c r="K40" s="1"/>
+      <c r="L40" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M40" s="1">
@@ -5709,10 +5648,10 @@
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A41" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C41" s="1">
         <v>108</v>
@@ -5727,22 +5666,20 @@
       <c r="F41" s="2">
         <v>6</v>
       </c>
-      <c r="G41" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="I41" s="19" t="s">
+      <c r="G41" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="I41" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J41" s="20" t="s">
+      <c r="J41" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K41" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L41" s="19" t="s">
+      <c r="K41" s="1"/>
+      <c r="L41" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M41" s="1">
@@ -5754,10 +5691,10 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A42" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C42" s="1">
         <v>109</v>
@@ -5769,22 +5706,20 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G42" s="19" t="s">
+      <c r="G42" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H42" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="I42" s="19" t="s">
+      <c r="H42" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="I42" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J42" s="20" t="s">
+      <c r="J42" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K42" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L42" s="19" t="s">
+      <c r="K42" s="1"/>
+      <c r="L42" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M42" s="1">
@@ -5796,10 +5731,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A43" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C43" s="1">
         <v>110</v>
@@ -5811,20 +5746,20 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G43" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H43" s="6"/>
-      <c r="I43" s="19" t="s">
+      <c r="G43" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="I43" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J43" s="20" t="s">
+      <c r="J43" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K43" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L43" s="19" t="s">
+      <c r="K43" s="1"/>
+      <c r="L43" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M43" s="1">
@@ -5836,10 +5771,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A44" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C44" s="1">
         <v>111</v>
@@ -5851,20 +5786,20 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G44" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H44" s="6"/>
-      <c r="I44" s="19" t="s">
+      <c r="G44" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="I44" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J44" s="20" t="s">
+      <c r="J44" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K44" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L44" s="19" t="s">
+      <c r="K44" s="1"/>
+      <c r="L44" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M44" s="1">
@@ -5876,10 +5811,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A45" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C45" s="1">
         <v>112</v>
@@ -5891,20 +5826,20 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G45" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H45" s="6"/>
-      <c r="I45" s="19" t="s">
+      <c r="G45" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="I45" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J45" s="20" t="s">
+      <c r="J45" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K45" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L45" s="19" t="s">
+      <c r="K45" s="1"/>
+      <c r="L45" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M45" s="1">
@@ -5916,10 +5851,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A46" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C46" s="1">
         <v>113</v>
@@ -5931,20 +5866,20 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="G46" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H46" s="6"/>
-      <c r="I46" s="19" t="s">
+      <c r="G46" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="I46" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J46" s="20" t="s">
+      <c r="J46" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K46" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L46" s="19" t="s">
+      <c r="K46" s="1"/>
+      <c r="L46" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M46" s="1">
@@ -5956,10 +5891,10 @@
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A47" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C47" s="1">
         <v>114</v>
@@ -5974,20 +5909,20 @@
       <c r="F47" s="2">
         <v>7</v>
       </c>
-      <c r="G47" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="H47" s="8"/>
-      <c r="I47" s="19" t="s">
+      <c r="G47" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="I47" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J47" s="20" t="s">
+      <c r="J47" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K47" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L47" s="21" t="s">
+      <c r="K47" s="1"/>
+      <c r="L47" s="19" t="s">
         <v>19</v>
       </c>
       <c r="M47" s="1">
@@ -5999,10 +5934,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A48" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C48" s="1">
         <v>115</v>
@@ -6014,20 +5949,20 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G48" s="19" t="s">
+      <c r="G48" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H48" s="6"/>
-      <c r="I48" s="19" t="s">
+      <c r="H48" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="I48" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J48" s="20" t="s">
+      <c r="J48" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K48" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L48" s="19" t="s">
+      <c r="K48" s="1"/>
+      <c r="L48" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M48" s="1">
@@ -6039,10 +5974,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C49" s="1">
         <v>116</v>
@@ -6054,20 +5989,20 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G49" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H49" s="6"/>
-      <c r="I49" s="19" t="s">
+      <c r="G49" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="I49" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J49" s="20" t="s">
+      <c r="J49" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K49" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L49" s="19" t="s">
+      <c r="K49" s="1"/>
+      <c r="L49" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M49" s="1">
@@ -6079,10 +6014,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A50" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C50" s="1">
         <v>117</v>
@@ -6094,20 +6029,20 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G50" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H50" s="6"/>
-      <c r="I50" s="19" t="s">
+      <c r="G50" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="I50" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J50" s="20" t="s">
+      <c r="J50" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K50" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L50" s="19" t="s">
+      <c r="K50" s="1"/>
+      <c r="L50" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M50" s="1">
@@ -6119,10 +6054,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A51" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C51" s="1">
         <v>118</v>
@@ -6134,20 +6069,20 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G51" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H51" s="6"/>
-      <c r="I51" s="19" t="s">
+      <c r="G51" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H51" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="I51" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J51" s="20" t="s">
+      <c r="J51" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K51" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L51" s="19" t="s">
+      <c r="K51" s="1"/>
+      <c r="L51" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M51" s="1">
@@ -6159,10 +6094,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A52" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C52" s="1">
         <v>119</v>
@@ -6174,20 +6109,20 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G52" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H52" s="6"/>
-      <c r="I52" s="19" t="s">
+      <c r="G52" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="I52" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J52" s="20" t="s">
+      <c r="J52" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K52" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L52" s="19" t="s">
+      <c r="K52" s="1"/>
+      <c r="L52" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M52" s="1">
@@ -6199,10 +6134,10 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A53" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C53" s="1">
         <v>120</v>
@@ -6217,20 +6152,20 @@
       <c r="F53" s="2">
         <v>8</v>
       </c>
-      <c r="G53" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="H53" s="8"/>
-      <c r="I53" s="19" t="s">
+      <c r="G53" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="I53" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J53" s="20" t="s">
+      <c r="J53" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K53" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L53" s="21" t="s">
+      <c r="K53" s="1"/>
+      <c r="L53" s="19" t="s">
         <v>19</v>
       </c>
       <c r="M53" s="1">
@@ -6242,10 +6177,10 @@
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A54" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C54" s="1">
         <v>121</v>
@@ -6257,19 +6192,20 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G54" s="19" t="s">
+      <c r="G54" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="I54" s="19" t="s">
+      <c r="H54" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="I54" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J54" s="20" t="s">
+      <c r="J54" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K54" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L54" s="25" t="s">
+      <c r="K54" s="1"/>
+      <c r="L54" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M54" s="1">
@@ -6281,10 +6217,10 @@
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A55" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C55" s="1">
         <v>122</v>
@@ -6296,19 +6232,20 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G55" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="I55" s="19" t="s">
+      <c r="G55" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="I55" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J55" s="20" t="s">
+      <c r="J55" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K55" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L55" s="25" t="s">
+      <c r="K55" s="1"/>
+      <c r="L55" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M55" s="1">
@@ -6320,10 +6257,10 @@
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A56" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C56" s="1">
         <v>123</v>
@@ -6335,19 +6272,20 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G56" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="I56" s="19" t="s">
+      <c r="G56" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="I56" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J56" s="20" t="s">
+      <c r="J56" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K56" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L56" s="25" t="s">
+      <c r="K56" s="1"/>
+      <c r="L56" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M56" s="1">
@@ -6359,10 +6297,10 @@
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A57" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C57" s="1">
         <v>124</v>
@@ -6374,19 +6312,20 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G57" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="I57" s="19" t="s">
+      <c r="G57" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H57" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="I57" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J57" s="20" t="s">
+      <c r="J57" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K57" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L57" s="25" t="s">
+      <c r="K57" s="1"/>
+      <c r="L57" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M57" s="1">
@@ -6398,10 +6337,10 @@
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A58" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C58" s="1">
         <v>125</v>
@@ -6413,19 +6352,20 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="G58" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="I58" s="19" t="s">
+      <c r="G58" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H58" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="I58" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J58" s="20" t="s">
+      <c r="J58" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K58" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L58" s="25" t="s">
+      <c r="K58" s="1"/>
+      <c r="L58" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M58" s="1">
@@ -6437,10 +6377,10 @@
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A59" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C59" s="1">
         <v>126</v>
@@ -6455,19 +6395,20 @@
       <c r="F59" s="2">
         <v>9</v>
       </c>
-      <c r="G59" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="I59" s="19" t="s">
+      <c r="G59" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H59" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="I59" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J59" s="20" t="s">
+      <c r="J59" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K59" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L59" s="21" t="s">
+      <c r="K59" s="1"/>
+      <c r="L59" s="19" t="s">
         <v>19</v>
       </c>
       <c r="M59" s="1">
@@ -6479,10 +6420,10 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A60" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C60" s="1">
         <v>127</v>
@@ -6494,19 +6435,20 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G60" s="19" t="s">
+      <c r="G60" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="I60" s="19" t="s">
+      <c r="H60" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I60" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J60" s="20" t="s">
+      <c r="J60" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K60" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L60" s="26" t="s">
+      <c r="K60" s="1"/>
+      <c r="L60" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M60" s="1">
@@ -6518,10 +6460,10 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A61" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C61" s="1">
         <v>128</v>
@@ -6533,19 +6475,20 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G61" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="I61" s="19" t="s">
+      <c r="G61" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H61" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I61" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J61" s="20" t="s">
+      <c r="J61" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K61" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L61" s="26" t="s">
+      <c r="K61" s="1"/>
+      <c r="L61" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M61" s="1">
@@ -6557,10 +6500,10 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A62" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C62" s="1">
         <v>129</v>
@@ -6572,19 +6515,20 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G62" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="I62" s="19" t="s">
+      <c r="G62" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H62" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I62" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J62" s="20" t="s">
+      <c r="J62" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K62" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L62" s="26" t="s">
+      <c r="K62" s="1"/>
+      <c r="L62" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M62" s="1">
@@ -6596,10 +6540,10 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A63" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C63" s="1">
         <v>130</v>
@@ -6611,19 +6555,20 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G63" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="I63" s="19" t="s">
+      <c r="G63" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H63" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I63" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J63" s="20" t="s">
+      <c r="J63" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K63" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L63" s="26" t="s">
+      <c r="K63" s="1"/>
+      <c r="L63" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M63" s="1">
@@ -6635,10 +6580,10 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A64" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C64" s="1">
         <v>131</v>
@@ -6650,19 +6595,20 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="G64" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="I64" s="19" t="s">
+      <c r="G64" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H64" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I64" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J64" s="20" t="s">
+      <c r="J64" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K64" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L64" s="26" t="s">
+      <c r="K64" s="1"/>
+      <c r="L64" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M64" s="1">
@@ -6674,10 +6620,10 @@
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A65" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C65" s="1">
         <v>132</v>
@@ -6692,19 +6638,20 @@
       <c r="F65" s="2">
         <v>10</v>
       </c>
-      <c r="G65" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="I65" s="19" t="s">
+      <c r="G65" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H65" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I65" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J65" s="20" t="s">
+      <c r="J65" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K65" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L65" s="21" t="s">
+      <c r="K65" s="1"/>
+      <c r="L65" s="19" t="s">
         <v>19</v>
       </c>
       <c r="M65" s="1">
@@ -6716,10 +6663,10 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A66" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C66" s="1">
         <v>133</v>
@@ -6731,20 +6678,20 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G66" s="19" t="s">
+      <c r="G66" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="H66" s="17"/>
-      <c r="I66" s="19" t="s">
+      <c r="H66" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="I66" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J66" s="20" t="s">
+      <c r="J66" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K66" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L66" s="26" t="s">
+      <c r="K66" s="1"/>
+      <c r="L66" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M66" s="1">
@@ -6756,10 +6703,10 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A67" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C67" s="1">
         <v>134</v>
@@ -6771,20 +6718,20 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G67" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="H67" s="17"/>
-      <c r="I67" s="19" t="s">
+      <c r="G67" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H67" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="I67" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J67" s="20" t="s">
+      <c r="J67" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K67" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L67" s="26" t="s">
+      <c r="K67" s="1"/>
+      <c r="L67" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M67" s="1">
@@ -6796,10 +6743,10 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A68" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C68" s="1">
         <v>135</v>
@@ -6811,20 +6758,20 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G68" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="H68" s="17"/>
-      <c r="I68" s="19" t="s">
+      <c r="G68" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H68" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="I68" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J68" s="20" t="s">
+      <c r="J68" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K68" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L68" s="26" t="s">
+      <c r="K68" s="1"/>
+      <c r="L68" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M68" s="1">
@@ -6836,10 +6783,10 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A69" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C69" s="1">
         <v>136</v>
@@ -6851,20 +6798,20 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G69" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="H69" s="17"/>
-      <c r="I69" s="19" t="s">
+      <c r="G69" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H69" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="I69" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J69" s="20" t="s">
+      <c r="J69" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K69" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L69" s="26" t="s">
+      <c r="K69" s="1"/>
+      <c r="L69" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M69" s="1">
@@ -6876,10 +6823,10 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A70" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C70" s="1">
         <v>137</v>
@@ -6891,20 +6838,20 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="G70" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="H70" s="17"/>
-      <c r="I70" s="19" t="s">
+      <c r="G70" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H70" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="I70" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J70" s="20" t="s">
+      <c r="J70" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K70" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L70" s="26" t="s">
+      <c r="K70" s="1"/>
+      <c r="L70" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M70" s="1">
@@ -6916,10 +6863,10 @@
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A71" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C71" s="1">
         <v>138</v>
@@ -6934,19 +6881,20 @@
       <c r="F71" s="2">
         <v>11</v>
       </c>
-      <c r="G71" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="I71" s="19" t="s">
+      <c r="G71" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H71" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="I71" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J71" s="20" t="s">
+      <c r="J71" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K71" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L71" s="21" t="s">
+      <c r="K71" s="1"/>
+      <c r="L71" s="19" t="s">
         <v>19</v>
       </c>
       <c r="M71" s="1">
@@ -6958,10 +6906,10 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A72" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C72" s="1">
         <v>139</v>
@@ -6973,19 +6921,20 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G72" s="19" t="s">
+      <c r="G72" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="I72" s="19" t="s">
+      <c r="H72" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="I72" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J72" s="20" t="s">
+      <c r="J72" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K72" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L72" s="26" t="s">
+      <c r="K72" s="1"/>
+      <c r="L72" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M72" s="1">
@@ -6997,10 +6946,10 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A73" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C73" s="1">
         <v>140</v>
@@ -7012,19 +6961,20 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G73" s="19" t="s">
-        <v>251</v>
-      </c>
-      <c r="I73" s="19" t="s">
+      <c r="G73" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="H73" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="I73" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J73" s="20" t="s">
+      <c r="J73" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K73" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L73" s="26" t="s">
+      <c r="K73" s="1"/>
+      <c r="L73" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M73" s="1">
@@ -7036,10 +6986,10 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A74" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C74" s="1">
         <v>141</v>
@@ -7051,19 +7001,20 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G74" s="19" t="s">
-        <v>252</v>
-      </c>
-      <c r="I74" s="19" t="s">
+      <c r="G74" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="H74" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="I74" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J74" s="20" t="s">
+      <c r="J74" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K74" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L74" s="26" t="s">
+      <c r="K74" s="1"/>
+      <c r="L74" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M74" s="1">
@@ -7075,10 +7026,10 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A75" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="1">
         <v>142</v>
@@ -7090,19 +7041,20 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="G75" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="I75" s="19" t="s">
+      <c r="G75" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="H75" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="I75" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J75" s="20" t="s">
+      <c r="J75" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K75" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L75" s="26" t="s">
+      <c r="K75" s="1"/>
+      <c r="L75" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M75" s="1">
@@ -7114,10 +7066,10 @@
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A76" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C76" s="1">
         <v>143</v>
@@ -7129,19 +7081,20 @@
         <f>E70+1</f>
         <v>24</v>
       </c>
-      <c r="G76" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="I76" s="19" t="s">
+      <c r="G76" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="H76" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="I76" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J76" s="20" t="s">
+      <c r="J76" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K76" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L76" s="26" t="s">
+      <c r="K76" s="1"/>
+      <c r="L76" s="21" t="s">
         <v>19</v>
       </c>
       <c r="M76" s="1">
@@ -7153,10 +7106,10 @@
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A77" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C77" s="1">
         <v>144</v>
@@ -7171,19 +7124,20 @@
       <c r="F77" s="1">
         <v>12</v>
       </c>
-      <c r="G77" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="I77" s="19" t="s">
+      <c r="G77" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="H77" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="I77" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="J77" s="20" t="s">
+      <c r="J77" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="K77" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="L77" s="19" t="s">
+      <c r="K77" s="1"/>
+      <c r="L77" s="17" t="s">
         <v>19</v>
       </c>
       <c r="M77" s="1">

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -4519,7 +4519,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G11" s="19" t="s">
         <v>254</v>
@@ -4726,7 +4726,7 @@
         <v>14</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G17" s="19" t="s">
         <v>254</v>
@@ -4935,7 +4935,7 @@
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G23" s="19" t="s">
         <v>254</v>
@@ -5178,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G29" s="19" t="s">
         <v>254</v>
@@ -5421,7 +5421,7 @@
         <v>17</v>
       </c>
       <c r="F35" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G35" s="19" t="s">
         <v>254</v>
@@ -5664,7 +5664,7 @@
         <v>18</v>
       </c>
       <c r="F41" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G41" s="19" t="s">
         <v>254</v>
@@ -5907,7 +5907,7 @@
         <v>19</v>
       </c>
       <c r="F47" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G47" s="19" t="s">
         <v>254</v>
@@ -6150,7 +6150,7 @@
         <v>20</v>
       </c>
       <c r="F53" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G53" s="19" t="s">
         <v>254</v>
@@ -6393,7 +6393,7 @@
         <v>21</v>
       </c>
       <c r="F59" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G59" s="19" t="s">
         <v>254</v>
@@ -6636,7 +6636,7 @@
         <v>22</v>
       </c>
       <c r="F65" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>254</v>
@@ -6879,7 +6879,7 @@
         <v>23</v>
       </c>
       <c r="F71" s="2">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G71" s="19" t="s">
         <v>254</v>
@@ -7122,7 +7122,7 @@
         <v>24</v>
       </c>
       <c r="F77" s="1">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>254</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="267">
   <si>
     <t>_Id</t>
   </si>
@@ -870,16 +870,16 @@
     <t>3,0,0,0</t>
   </si>
   <si>
+    <t>4,0,0,0</t>
+  </si>
+  <si>
+    <t>5,0,0,0</t>
+  </si>
+  <si>
+    <t>6,0,0,0</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>4,0,0,0</t>
-  </si>
-  <si>
-    <t>5,0,0,0</t>
-  </si>
-  <si>
-    <t>6,0,0,0</t>
   </si>
   <si>
     <t>7,0,0,0</t>
@@ -4961,12 +4961,8 @@
       </c>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A24" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>257</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
       <c r="C24" s="1">
         <v>91</v>
       </c>
@@ -4981,7 +4977,7 @@
         <v>246</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>248</v>
@@ -5001,12 +4997,6 @@
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A25" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C25" s="1">
         <v>92</v>
       </c>
@@ -5021,7 +5011,7 @@
         <v>250</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I25" s="17" t="s">
         <v>248</v>
@@ -5041,12 +5031,6 @@
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A26" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C26" s="1">
         <v>93</v>
       </c>
@@ -5061,7 +5045,7 @@
         <v>251</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I26" s="17" t="s">
         <v>248</v>
@@ -5081,12 +5065,6 @@
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A27" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C27" s="1">
         <v>94</v>
       </c>
@@ -5101,7 +5079,7 @@
         <v>252</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I27" s="17" t="s">
         <v>248</v>
@@ -5121,12 +5099,6 @@
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A28" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C28" s="1">
         <v>95</v>
       </c>
@@ -5141,7 +5113,7 @@
         <v>253</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>248</v>
@@ -5161,12 +5133,8 @@
       </c>
     </row>
     <row r="29" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A29" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>257</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
       <c r="C29" s="1">
         <v>96</v>
       </c>
@@ -5184,7 +5152,7 @@
         <v>254</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I29" s="17" t="s">
         <v>248</v>
@@ -5204,12 +5172,8 @@
       </c>
     </row>
     <row r="30" s="3" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A30" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>257</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
       <c r="C30" s="1">
         <v>97</v>
       </c>
@@ -5224,7 +5188,7 @@
         <v>246</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>248</v>
@@ -5244,12 +5208,6 @@
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A31" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C31" s="1">
         <v>98</v>
       </c>
@@ -5264,7 +5222,7 @@
         <v>250</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I31" s="17" t="s">
         <v>248</v>
@@ -5284,12 +5242,6 @@
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A32" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C32" s="1">
         <v>99</v>
       </c>
@@ -5304,7 +5256,7 @@
         <v>251</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I32" s="17" t="s">
         <v>248</v>
@@ -5324,12 +5276,6 @@
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A33" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C33" s="1">
         <v>100</v>
       </c>
@@ -5344,7 +5290,7 @@
         <v>252</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I33" s="17" t="s">
         <v>248</v>
@@ -5364,12 +5310,6 @@
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A34" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C34" s="1">
         <v>101</v>
       </c>
@@ -5384,7 +5324,7 @@
         <v>253</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>248</v>
@@ -5404,12 +5344,8 @@
       </c>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A35" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>257</v>
-      </c>
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
       <c r="C35" s="1">
         <v>102</v>
       </c>
@@ -5427,7 +5363,7 @@
         <v>254</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I35" s="17" t="s">
         <v>248</v>
@@ -5447,12 +5383,6 @@
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A36" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C36" s="1">
         <v>103</v>
       </c>
@@ -5467,7 +5397,7 @@
         <v>246</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>248</v>
@@ -5487,12 +5417,6 @@
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A37" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C37" s="1">
         <v>104</v>
       </c>
@@ -5507,7 +5431,7 @@
         <v>250</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I37" s="17" t="s">
         <v>248</v>
@@ -5527,12 +5451,6 @@
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A38" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C38" s="1">
         <v>105</v>
       </c>
@@ -5547,7 +5465,7 @@
         <v>251</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I38" s="17" t="s">
         <v>248</v>
@@ -5567,12 +5485,6 @@
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A39" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C39" s="1">
         <v>106</v>
       </c>
@@ -5587,7 +5499,7 @@
         <v>252</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I39" s="17" t="s">
         <v>248</v>
@@ -5607,12 +5519,6 @@
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A40" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C40" s="1">
         <v>107</v>
       </c>
@@ -5627,7 +5533,7 @@
         <v>253</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I40" s="17" t="s">
         <v>248</v>
@@ -5647,12 +5553,8 @@
       </c>
     </row>
     <row r="41" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A41" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>257</v>
-      </c>
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
       <c r="C41" s="1">
         <v>108</v>
       </c>
@@ -5670,7 +5572,7 @@
         <v>254</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I41" s="17" t="s">
         <v>248</v>
@@ -5691,10 +5593,10 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A42" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C42" s="1">
         <v>109</v>
@@ -5731,10 +5633,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A43" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C43" s="1">
         <v>110</v>
@@ -5771,10 +5673,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A44" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C44" s="1">
         <v>111</v>
@@ -5811,10 +5713,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A45" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C45" s="1">
         <v>112</v>
@@ -5851,10 +5753,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A46" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C46" s="1">
         <v>113</v>
@@ -5891,10 +5793,10 @@
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A47" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C47" s="1">
         <v>114</v>
@@ -5934,10 +5836,10 @@
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A48" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C48" s="1">
         <v>115</v>
@@ -5974,10 +5876,10 @@
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A49" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C49" s="1">
         <v>116</v>
@@ -6014,10 +5916,10 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A50" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C50" s="1">
         <v>117</v>
@@ -6054,10 +5956,10 @@
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A51" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C51" s="1">
         <v>118</v>
@@ -6094,10 +5996,10 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A52" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C52" s="1">
         <v>119</v>
@@ -6134,10 +6036,10 @@
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A53" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C53" s="1">
         <v>120</v>
@@ -6177,10 +6079,10 @@
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A54" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C54" s="1">
         <v>121</v>
@@ -6217,10 +6119,10 @@
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A55" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C55" s="1">
         <v>122</v>
@@ -6257,10 +6159,10 @@
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A56" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C56" s="1">
         <v>123</v>
@@ -6297,10 +6199,10 @@
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A57" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C57" s="1">
         <v>124</v>
@@ -6337,10 +6239,10 @@
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A58" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C58" s="1">
         <v>125</v>
@@ -6377,10 +6279,10 @@
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A59" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C59" s="1">
         <v>126</v>
@@ -6420,10 +6322,10 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A60" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C60" s="1">
         <v>127</v>
@@ -6460,10 +6362,10 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A61" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C61" s="1">
         <v>128</v>
@@ -6500,10 +6402,10 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A62" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C62" s="1">
         <v>129</v>
@@ -6540,10 +6442,10 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A63" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C63" s="1">
         <v>130</v>
@@ -6580,10 +6482,10 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A64" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C64" s="1">
         <v>131</v>
@@ -6620,10 +6522,10 @@
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A65" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C65" s="1">
         <v>132</v>
@@ -6663,10 +6565,10 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A66" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C66" s="1">
         <v>133</v>
@@ -6703,10 +6605,10 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A67" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C67" s="1">
         <v>134</v>
@@ -6743,10 +6645,10 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A68" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C68" s="1">
         <v>135</v>
@@ -6783,10 +6685,10 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A69" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C69" s="1">
         <v>136</v>
@@ -6823,10 +6725,10 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A70" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C70" s="1">
         <v>137</v>
@@ -6863,10 +6765,10 @@
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A71" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C71" s="1">
         <v>138</v>
@@ -6906,10 +6808,10 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A72" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C72" s="1">
         <v>139</v>
@@ -6946,10 +6848,10 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A73" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C73" s="1">
         <v>140</v>
@@ -6986,10 +6888,10 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A74" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C74" s="1">
         <v>141</v>
@@ -7026,10 +6928,10 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A75" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C75" s="1">
         <v>142</v>
@@ -7066,10 +6968,10 @@
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A76" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C76" s="1">
         <v>143</v>
@@ -7106,10 +7008,10 @@
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A77" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C77" s="1">
         <v>144</v>

--- a/Excel/MapConfig.xlsx
+++ b/Excel/MapConfig.xlsx
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="267">
   <si>
     <t>_Id</t>
   </si>
@@ -879,16 +879,16 @@
     <t>6,0,0,0</t>
   </si>
   <si>
+    <t>7,0,0,0</t>
+  </si>
+  <si>
+    <t>8,0,0,0</t>
+  </si>
+  <si>
+    <t>9,0,0,0</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>7,0,0,0</t>
-  </si>
-  <si>
-    <t>8,0,0,0</t>
-  </si>
-  <si>
-    <t>9,0,0,0</t>
   </si>
   <si>
     <t>10,0,0,0</t>
@@ -5592,12 +5592,6 @@
       </c>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A42" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C42" s="1">
         <v>109</v>
       </c>
@@ -5612,7 +5606,7 @@
         <v>246</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I42" s="17" t="s">
         <v>248</v>
@@ -5632,12 +5626,6 @@
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A43" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C43" s="1">
         <v>110</v>
       </c>
@@ -5652,7 +5640,7 @@
         <v>250</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I43" s="17" t="s">
         <v>248</v>
@@ -5672,12 +5660,6 @@
       </c>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A44" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C44" s="1">
         <v>111</v>
       </c>
@@ -5692,7 +5674,7 @@
         <v>251</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>248</v>
@@ -5712,12 +5694,6 @@
       </c>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A45" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C45" s="1">
         <v>112</v>
       </c>
@@ -5732,7 +5708,7 @@
         <v>252</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I45" s="17" t="s">
         <v>248</v>
@@ -5752,12 +5728,6 @@
       </c>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A46" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C46" s="1">
         <v>113</v>
       </c>
@@ -5772,7 +5742,7 @@
         <v>253</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I46" s="17" t="s">
         <v>248</v>
@@ -5792,12 +5762,8 @@
       </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A47" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>260</v>
-      </c>
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
       <c r="C47" s="1">
         <v>114</v>
       </c>
@@ -5815,7 +5781,7 @@
         <v>254</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I47" s="17" t="s">
         <v>248</v>
@@ -5835,12 +5801,6 @@
       </c>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A48" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C48" s="1">
         <v>115</v>
       </c>
@@ -5855,7 +5815,7 @@
         <v>246</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I48" s="17" t="s">
         <v>248</v>
@@ -5875,12 +5835,6 @@
       </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A49" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C49" s="1">
         <v>116</v>
       </c>
@@ -5895,7 +5849,7 @@
         <v>250</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I49" s="17" t="s">
         <v>248</v>
@@ -5915,12 +5869,6 @@
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A50" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C50" s="1">
         <v>117</v>
       </c>
@@ -5935,7 +5883,7 @@
         <v>251</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I50" s="17" t="s">
         <v>248</v>
@@ -5955,12 +5903,6 @@
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A51" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C51" s="1">
         <v>118</v>
       </c>
@@ -5975,7 +5917,7 @@
         <v>252</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I51" s="17" t="s">
         <v>248</v>
@@ -5995,12 +5937,6 @@
       </c>
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A52" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C52" s="1">
         <v>119</v>
       </c>
@@ -6015,7 +5951,7 @@
         <v>253</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I52" s="17" t="s">
         <v>248</v>
@@ -6035,12 +5971,8 @@
       </c>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A53" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>260</v>
-      </c>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
       <c r="C53" s="1">
         <v>120</v>
       </c>
@@ -6058,7 +5990,7 @@
         <v>254</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I53" s="17" t="s">
         <v>248</v>
@@ -6078,12 +6010,6 @@
       </c>
     </row>
     <row r="54" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A54" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C54" s="1">
         <v>121</v>
       </c>
@@ -6098,7 +6024,7 @@
         <v>246</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I54" s="17" t="s">
         <v>248</v>
@@ -6118,12 +6044,6 @@
       </c>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A55" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C55" s="1">
         <v>122</v>
       </c>
@@ -6138,7 +6058,7 @@
         <v>250</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I55" s="17" t="s">
         <v>248</v>
@@ -6158,12 +6078,6 @@
       </c>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A56" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C56" s="1">
         <v>123</v>
       </c>
@@ -6178,7 +6092,7 @@
         <v>251</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I56" s="17" t="s">
         <v>248</v>
@@ -6198,12 +6112,6 @@
       </c>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A57" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C57" s="1">
         <v>124</v>
       </c>
@@ -6218,7 +6126,7 @@
         <v>252</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I57" s="17" t="s">
         <v>248</v>
@@ -6238,12 +6146,6 @@
       </c>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A58" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="C58" s="1">
         <v>125</v>
       </c>
@@ -6258,7 +6160,7 @@
         <v>253</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I58" s="17" t="s">
         <v>248</v>
@@ -6278,12 +6180,8 @@
       </c>
     </row>
     <row r="59" s="2" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A59" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>260</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
       <c r="C59" s="1">
         <v>126</v>
       </c>
@@ -6301,7 +6199,7 @@
         <v>254</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I59" s="17" t="s">
         <v>248</v>
@@ -6322,10 +6220,10 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A60" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C60" s="1">
         <v>127</v>
@@ -6362,10 +6260,10 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A61" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C61" s="1">
         <v>128</v>
@@ -6402,10 +6300,10 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A62" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C62" s="1">
         <v>129</v>
@@ -6442,10 +6340,10 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A63" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C63" s="1">
         <v>130</v>
@@ -6482,10 +6380,10 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A64" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C64" s="1">
         <v>131</v>
@@ -6522,10 +6420,10 @@
     </row>
     <row r="65" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A65" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C65" s="1">
         <v>132</v>
@@ -6565,10 +6463,10 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A66" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C66" s="1">
         <v>133</v>
@@ -6605,10 +6503,10 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A67" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C67" s="1">
         <v>134</v>
@@ -6645,10 +6543,10 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A68" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C68" s="1">
         <v>135</v>
@@ -6685,10 +6583,10 @@
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A69" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C69" s="1">
         <v>136</v>
@@ -6725,10 +6623,10 @@
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A70" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C70" s="1">
         <v>137</v>
@@ -6765,10 +6663,10 @@
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="1:14">
       <c r="A71" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C71" s="1">
         <v>138</v>
@@ -6808,10 +6706,10 @@
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A72" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C72" s="1">
         <v>139</v>
@@ -6848,10 +6746,10 @@
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A73" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C73" s="1">
         <v>140</v>
@@ -6888,10 +6786,10 @@
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A74" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C74" s="1">
         <v>141</v>
@@ -6928,10 +6826,10 @@
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A75" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C75" s="1">
         <v>142</v>
@@ -6968,10 +6866,10 @@
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A76" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C76" s="1">
         <v>143</v>
@@ -7008,10 +6906,10 @@
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A77" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C77" s="1">
         <v>144</v>
